--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -583,7 +583,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>28 contracts, 1,007 operations, 378 tables. The data boundaries were drawn first and the service boundaries follow them — no service spans a schema it does not own, and no schema is written by two services.</t>
+          <t>28 contracts, 1,007 operations, 379 tables. The data boundaries were drawn first and the service boundaries follow them — no service spans a schema it does not own, and no schema is written by two services.</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>**`platform.scope_node` is reached by 304 of 379 tables** — the tenancy spine. Workforce and approvals are folded in because each is small, both read `scope_node` constantly and write it rarely, and splitting them means three services doing the same joins.
+          <t>**`platform.org_unit` is reached by 304 of 379 tables** — the tenancy spine. Workforce and approvals are folded in because each is small, both read `org_unit` constantly and write it rarely, and splitting them means three services doing the same joins.
 **`shift` was folded in here on 24 August and moved to OrderService the same day.** The reasoning was that a shift owns no tables of its own — which is true — and the conclusion was wrong. **A service with no data belongs where its data is**, and a shift's data is entirely in `orders`: `orders.shift`, `orders.deposit_box`, `orders.cash_movement`, `orders.cash_count_line`.
 **The coupling made it visible.** All 43 of Tenancy's cross-service touches into `orders` were the `shift` contract — 19 writes and 24 reads, the heaviest coupling in the platform, created to solve a cosmetic problem.</t>
         </is>
@@ -828,7 +828,7 @@
         <is>
           <t>**The transactional core.** 96 operations, 34 tables, and the highest write rate in the platform. Separate because its scaling profile is unlike anything else — a Saturday evening is ten times a Tuesday morning.
 **`shift` belongs here and not in Tenancy.** A shift is venue-scoped, which is what made it look like a tenancy concern — but **venue scope is the platform's default rather than a service boundary**: 675 of 1,014 operations are venue-scoped.
-**What decides the service is who owns the tables.** A shift holds cash, `orders.deposit_box` reconciles against payments, and `orders.cash_movement` posts to `ledger.entry` at close. **A till's takings and a till's drawer are the same money counted twice** — separating them makes every settlement a distributed join.</t>
+**What decides the service is who owns the tables.** A shift holds cash, `orders.deposit_box` reconciles against payments, and `orders.cash_movement` posts to `ledger.posting` at close. **A till's takings and a till's drawer are the same money counted twice** — separating them makes every settlement a distributed join.</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1230,7 +1230,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>ControlService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>CrossCellService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>cross-cell</t>
+          <t>cross-region</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>cross-cell, identity, marketing-crm, subscription, tenancy, venue-map +1</t>
+          <t>cross-region, identity, marketing-crm, subscription, tenancy, venue-map +1</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>ai, maintenance, venue-map</t>
+          <t>ai, maintenance, seating, venue-map</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1678,11 +1678,11 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>ControlService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, resources, shift</t>
+          <t>fnb, identity, marketing-crm, orders, resources, shift, subscription</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>access, catalogue, finance, promotions, subscription</t>
+          <t>access, catalogue, finance, promotions</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2041,17 +2041,17 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>cross-cell, identity, inventory, tenancy</t>
+          <t>access, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, platform-ops, shift, subscription, tenancy, white-label</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>ai, approvals, catalogue, finance, fnb, marketing-crm +8</t>
+          <t>ai, public-api, resources, retail, venue-map, workforce</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.scope_node` is reached by 289 of 378 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
+          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.org_unit` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -2268,12 +2268,12 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>sync</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>CrossCellService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
@@ -2284,70 +2284,66 @@
           <t>postgres</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>access, games</t>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>subscription</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>venuemap</t>
+          <t>sync</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>venue-map</t>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>access, games, subscription</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>access, ai, marketing-crm, workforce</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>whitelabel</t>
+          <t>venuemap</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>WhiteLabelService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -2356,52 +2352,87 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>white-label</t>
+          <t>venue-map</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>access, ai, marketing-crm, workforce</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
+          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
+          <t>whitelabel</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>WhiteLabelService</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>white-label</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>TenancyService</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="C31" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Rotas, attendance, announcements, incidents. Small, venue-scoped, and folded into TenancyService because it reads `scope_node` constantly.</t>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Rotas, attendance, announcements, incidents. Small, venue-scoped, and folded into TenancyService because it reads `org_unit` constantly.</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2470,42 +2501,42 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>marketing.message_dispatch</t>
+          <t>platform.outbox</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, public-api, workforce</t>
+          <t>access, approvals, catalogue, finance, fnb, inventory, maintenance, marketing-crm, orders, platform-ops, shift, subscription, white-label</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>**Five writers, and every one is sending a message somebody asked for.** A verification email, a payment link, an evacuation notice.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>access.entitlement</t>
+          <t>marketing.message_dispatch</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>AccessService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>access, catalogue, orders</t>
+          <t>fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
@@ -2513,149 +2544,149 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
+          <t>**Five writers, and every one is sending a message somebody asked for.** A verification email, a payment link, an evacuation notice.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ledger.entry</t>
+          <t>access.entitlement</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>AccessService</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>access, catalogue, orders</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>**A till closing is a ledger act.** Settling a shift posts to the ledger, and a payment writes its own entry — appending, never redefining.</t>
+          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>ledger.journal_entry</t>
+          <t>orders.order_line</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>fnb, orders, subscription</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>As above. The journal is written by whatever caused the money to move.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>identity.grant</t>
+          <t>orders.sales_order</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>identity, orders, public-api</t>
+          <t>identity, orders, subscription</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
+          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>inventory.movement</t>
+          <t>ledger.journal_entry</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>fnb, inventory, retail</t>
+          <t>finance, orders, shift</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
+          <t>As above. The journal is written by whatever caused the money to move.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>approvals.request</t>
+          <t>ledger.posting</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription, workforce</t>
+          <t>finance, orders, shift</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**A till closing is a ledger act.** Settling a shift posts to the ledger, and a payment writes its own entry — appending, never redefining.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>marketing.consent_record</t>
+          <t>sync.rejection</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>access, marketing-crm, orders</t>
+          <t>access, games, subscription</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
@@ -2670,71 +2701,71 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>orders.stored_value_authorisation</t>
+          <t>identity.delegated_access</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>marketing-crm, orders, resources</t>
+          <t>identity, orders, public-api</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>catalogue.product</t>
+          <t>inventory.movement</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>fnb, inventory, retail</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>catalogue.inventory_lease</t>
+          <t>approvals.request</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>catalogue, orders</t>
+          <t>approvals, subscription, workforce</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -2745,21 +2776,21 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>orders.order_line</t>
+          <t>marketing.consent_record</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>fnb, orders</t>
+          <t>access, marketing-crm, orders</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -2770,7 +2801,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>orders.sales_order</t>
+          <t>orders.stored_value_authorisation</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -2780,36 +2811,36 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>identity, orders</t>
+          <t>marketing-crm, orders, resources</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>sync.rejection</t>
+          <t>catalogue.product</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>CrossCellService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>access, games</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -2820,21 +2851,21 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>platform.dsar_request</t>
+          <t>catalogue.inventory_hold</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>cross-cell, identity</t>
+          <t>catalogue, orders</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -2845,46 +2876,46 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>pii.subject</t>
+          <t>platform.region_settings</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>finance, tenancy</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>orders.payment</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>orders, subscription</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -2895,71 +2926,71 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ai.interaction</t>
+          <t>platform.dsar_request</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>cross-region, identity</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>retail.wallet_transaction</t>
+          <t>pii.subject</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>RetailService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>orders, retail</t>
+          <t>identity, marketing-crm</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -2970,48 +3001,123 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>ai.interaction</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
+          <t>retail.wallet_transaction</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>RetailService</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>orders, retail</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>catalogue.product_version</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>CatalogueService</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>catalogue, fnb</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>catalogue.price</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>CatalogueService</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>fnb, inventory</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>platform.audit_record</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>TenancyService</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>inventory, tenancy</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D29" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
@@ -3082,7 +3188,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>**First and alone.** Twelve contracts read identity and 289 tables anchor on `platform.scope_node` — a restart here is an outage everywhere.</t>
+          <t>**First and alone.** Twelve contracts read identity and 289 tables anchor on `platform.org_unit` — a restart here is an outage everywhere.</t>
         </is>
       </c>
     </row>
@@ -3157,12 +3263,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ControlService, WhiteLabelService, ReportingService, CrossCellService</t>
+          <t>PlatformService, WhiteLabelService, ReportingService, CrossRegionService</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>**Control is needed to provision a tenant and not to serve one.** Reporting reads the replica. CrossCell only matters once a second region exists.</t>
+          <t>**Control is needed to provision a tenant and not to serve one.** Reporting reads the replica. CrossRegion only matters once a second region exists.</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3282,7 @@
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>MarketingService · AiService · ReportingService · CrossCellService</t>
+          <t>MarketingService · AiService · ReportingService · CrossRegionService</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3325,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>platform.scope_node is reached by 289 of 378 tables — the tenancy spine. Configuration resolves by walking the path upward until something answers.</t>
+          <t>platform.org_unit is reached by 289 of 379 tables — the tenancy spine. Configuration resolves by walking the path upward until something answers.</t>
         </is>
       </c>
     </row>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -1432,7 +1432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1533,156 +1533,152 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>accreditation</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>postgres, postgres-analytical</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>ai, reporting</t>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>accreditation</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>fnb, subscription, venue-map</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Conversations, interactions, proposed actions, knowledge, suggestions. **Only the AI contract writes these** (ADR-0020), and the boundary caught four wrongly-placed writes in one week.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>approvals</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>postgres, postgres-analytical</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>approvals, subscription, workforce</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>fnb, subscription, venue-map</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Approval requests and decisions. **One mechanism, not one per thing approved** — a write-off, a scenario and a price change are all requests with a subject.</t>
+          <t>Conversations, interactions, proposed actions, knowledge, suggestions. **Only the AI contract writes these** (ADR-0020), and the boundary caught four wrongly-placed writes in one week.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>assets</t>
+          <t>approvals</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>assets</t>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>approvals, subscription, workforce</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>ai, maintenance, seating, venue-map</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Media assets, usage, upload tickets. Cross-tenant sharing refused outside one tenant's own scope tree.</t>
+          <t>Approval requests and decisions. **One mechanism, not one per thing approved** — a write-off, a scenario and a price change are all requests with a subject.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>catalogue</t>
+          <t>assets</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>catalogue, fnb, inventory, orders</t>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>assets</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>access, ai, finance, games, marketing-crm, promotions +3</t>
+          <t>ai, maintenance, seating, venue-map</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Products, variants, prices, performances, inventory leases. **What is for sale.** Separate from `orders` because a product outlives every order against it, and a catalogue that lived in the order schema could not be published as a bundle.</t>
+          <t>Media assets, usage, upload tickets. Cross-tenant sharing refused outside one tenant's own scope tree.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>catalogue</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1691,68 +1687,68 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>marketing-crm, platform-ops, public-api, subscription, white-label</t>
+          <t>catalogue, fnb, inventory, orders</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>ai, finance</t>
+          <t>access, ai, finance, games, marketing-crm, promotions +3</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Tenants, plans, licences, cells, migrations, developer accounts. **Three contracts write it** — subscription, platform-ops and public-api — and that is correct: they are one bounded context with three API surfaces.</t>
+          <t>Products, variants, prices, performances, inventory leases. **What is for sale.** Separate from `orders` because a product outlives every order against it, and a catalogue that lived in the order schema could not be published as a bundle.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>fnb</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>FnbService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>fnb</t>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>marketing-crm, platform-ops, public-api, subscription, white-label</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>ai, inventory</t>
+          <t>ai, finance</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Outlets, menus, kitchen tickets, tables, recipes, food safety. **34 tables and the largest operational domain.** Separate because it is licensed separately and because the kitchen runs offline.</t>
+          <t>Tenants, plans, licences, cells, migrations, developer accounts. **Three contracts write it** — subscription, platform-ops and public-api — and that is correct: they are one bounded context with three API surfaces.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>fnb</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>FnbService</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1761,208 +1757,208 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>fnb</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ai, inventory</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Arcade, credit ledger, redemption. Fully optional, fully separate.</t>
+          <t>Outlets, menus, kitchen tickets, tables, recipes, food safety. **34 tables and the largest operational domain.** Separate because it is licensed separately and because the kitchen runs offline.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>identity</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>postgres, redis</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>identity, orders, public-api, tenancy</t>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>games</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>access, approvals, fnb, marketing-crm, reporting, resources +4</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Principals, roles, sessions, credentials. **Read by twelve contracts and reads almost nothing.** Separate because everything resolves a principal before it does anything else, and a schema that everything reads must be one nothing can lock.</t>
+          <t>Arcade, credit ledger, redemption. Fully optional, fully separate.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>identity</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>derived, postgres</t>
+          <t>postgres, redis</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>fnb, inventory, maintenance, retail</t>
+          <t>identity, orders, public-api, tenancy</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>access, approvals, fnb, marketing-crm, reporting, resources +4</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Items, movements, counts, requisitions, purchase orders, suppliers. **The level is derived from the movements** and never stored — a stored level and a movement ledger that disagree is a stock count nobody can reconcile.</t>
+          <t>Principals, roles, sessions, credentials. **Read by twelve contracts and reads almost nothing.** Separate because everything resolves a principal before it does anything else, and a schema that everything reads must be one nothing can lock.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>derived, postgres</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>fnb, inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>catalogue, inventory, subscription</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Journal entries, lines, accounts, settlements. **Append-only, never updated, never deleted.** A different discipline from everything around it, and one that should not share a schema with anything that mutates.</t>
+          <t>Items, movements, counts, requisitions, purchase orders, suppliers. **The level is derived from the movements** and never stored — a stored level and a movement ledger that disagree is a stock count nobody can reconcile.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>maintenance</t>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>finance, orders, shift</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>ai, resources</t>
+          <t>catalogue, inventory, subscription</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Assets, work orders, inspections. Separate from `platform.device` because **a turnstile is an asset and a workstation is a station** — one is maintained, the other is configured.</t>
+          <t>Journal entries, lines, accounts, settlements. **Append-only, never updated, never deleted.** A different discipline from everything around it, and one that should not share a schema with anything that mutates.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>access, fnb, identity, marketing-crm, orders, public-api, workforce</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>ai, catalogue, promotions, resources, white-label</t>
+          <t>ai, resources</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Guest profiles, segments, campaigns, consents, cases. **37 tables, the largest single schema.** Holds consent records, which is why it reads `pii` and never writes it.</t>
+          <t>Assets, work orders, inspections. Separate from `platform.device` because **a turnstile is an asset and a workstation is a station** — one is maintained, the other is configured.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -1971,33 +1967,33 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, resources, shift, subscription</t>
+          <t>access, fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>access, catalogue, finance, promotions</t>
+          <t>ai, catalogue, promotions, resources, white-label</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
+          <t>Guest profiles, segments, campaigns, consents, cases. **37 tables, the largest single schema.** Holds consent records, which is why it reads `pii` and never writes it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>pii</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2006,164 +2002,160 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>access, identity, marketing-crm</t>
+          <t>fnb, identity, marketing-crm, orders, resources, shift, subscription</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>fnb, orders, resources, retail</t>
+          <t>access, catalogue, finance, promotions</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Names, phones, emails, documents. **Separate from `identity` deliberately** (ADR-0023): a principal is who may act, a subject is who they are. **One writer only** — which is what makes a subject-access export and a deletion request answerable at all.</t>
+          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>access, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, platform-ops, shift, subscription, tenancy, white-label</t>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>payments</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>ai, public-api, resources, retail, venue-map, workforce</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.org_unit` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>pii</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>promotions</t>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>access, identity, marketing-crm</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>ai, marketing-crm, orders</t>
+          <t>fnb, orders, resources, retail</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
+          <t>Names, phones, emails, documents. **Separate from `identity` deliberately** (ADR-0023): a principal is who may act, a subject is who they are. **One writer only** — which is what makes a subject-access export and a deletion request answerable at all.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>queue</t>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>access, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, platform-ops, shift, subscription, tenancy, white-label</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>venue-map</t>
+          <t>ai, public-api, resources, retail, venue-map, workforce</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
+          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.org_unit` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>ReportingService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>derived, postgres</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, marketing-crm, orders</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
+          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -2181,77 +2173,73 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>venue-map</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
+          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>RetailService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>orders, retail</t>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>rental</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>ai, finance</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>ReportingService</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>derived, postgres</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
@@ -2261,54 +2249,58 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
+          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
+          <t>VenueOpsService</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>resources</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>subscription</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>sync</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>RetailService</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -2317,33 +2309,33 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>access, games, subscription</t>
+          <t>orders, retail</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>ai, finance</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
+          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>venuemap</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -2352,33 +2344,33 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>venue-map</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>access, ai, marketing-crm, workforce</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>whitelabel</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>WhiteLabelService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -2387,50 +2379,213 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>white-label</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>sync</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>CrossRegionService</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>access, games, subscription</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>tenancy</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>tenancy</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>venuemap</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>VenueOpsService</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>venue-map</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>access, ai, marketing-crm, workforce</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>wallet</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>wallet</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>whitelabel</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>WhiteLabelService</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>white-label</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>TenancyService</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="C36" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>Rotas, attendance, announcements, incidents. Small, venue-scoped, and folded into TenancyService because it reads `org_unit` constantly.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -112,17 +112,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FDECEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDECEC"/>
       </patternFill>
     </fill>
   </fills>
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>52</v>
+        <v>136</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>tenancy, workforce, approvals</t>
+          <t>tenancy, workforce, approvals, accreditation</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>132</v>
+        <v>389</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>orders, shift</t>
+          <t>orders, shift, payments</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>AccessService</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -854,46 +854,46 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>61%</t>
+        <v>8</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>57%</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>access</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>access</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>**Money, and it is append-only.** 54 operations over 18 tables that are never updated and never deleted — a different discipline from everything around it, and one that should not share a deploy with anything that does mutate.</t>
+          <t>**The gate.** Validating an entitlement is a sub-300ms decision made forty times a minute per lane, and it must work when the network does not.</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Write-heavy, batch-tolerant, not latency-critical. Recognition and revaluation are jobs.</t>
+          <t>Read-heavy, extreme latency sensitivity, edge-cached. **`frozenDays` is held rather than replayed** precisely because the gate cannot afford the arithmetic.</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>**Correctness over availability.** A ledger that is briefly unavailable is recoverable; one that is briefly wrong is not.</t>
+          <t>Down means the gates stop. Runs at the edge with a local decision cache.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>AccessService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -902,94 +902,94 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>57%</t>
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>61%</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>access</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>**The gate.** Validating an entitlement is a sub-300ms decision made forty times a minute per lane, and it must work when the network does not.</t>
+          <t>**Money, and it is append-only.** 54 operations over 18 tables that are never updated and never deleted — a different discipline from everything around it, and one that should not share a deploy with anything that does mutate.</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Read-heavy, extreme latency sensitivity, edge-cached. **`frozenDays` is held rather than replayed** precisely because the gate cannot afford the arithmetic.</t>
+          <t>Write-heavy, batch-tolerant, not latency-critical. Recognition and revaluation are jobs.</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Down means the gates stop. Runs at the edge with a local decision cache.</t>
+          <t>**Correctness over availability.** A ledger that is briefly unavailable is recoverable; one that is briefly wrong is not.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>operations</t>
+          <t>WalletService</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>commerce</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>47%</t>
+        <v>23</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>queue, maintenance, resources, venue-map, assets, games</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>queue, maintenance, resources, venuemap, assets, games</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>**Six small domains, 102 operations, one team.** Queue, maintenance, bookable resources, venue mapping, media assets and arcade. None is large enough to deploy alone, all are venue-scoped, none is on the critical sale path, and **all six are licensed as optional modules** — a venue that buys none of them should not be running six idle services.</t>
+          <t>**Eight domains need a wallet and none of them owns it.** A Gold Membership issues F&amp;B credit, parking credits and ride credits into the same wallet, so subscription, games and F&amp;B all read it; `getWalletLiability` aggregates outstanding value across every credit type, so it has to see all of them. The 13 wallet types in the client's library are compositions of owner, credit type and scope rather than thirteen kinds, which is only expressible in one place. **Split out of `retail` on 19 September**, where 13 of retail's 37 operations were the entire wallet runtime while `wallet.yaml` held only its rules.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Low and steady. Queue readings are the only frequent write.</t>
+          <t>Read-heavy on the sale path — every till and reader resolves a balance — and write-heavy on top-up. **Latency-critical in a way LedgerService is not**, which is why the two are separate: the ledger is append-only and batch-tolerant, a balance check is neither.</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Down degrades venue operations. Selling and admitting continue.</t>
+          <t>**It holds a liability owed to a customer.** A wallet that double-spends is a financial loss, not a bug report. Deduction order across credit lots is FEFO and is decided here, once, rather than per caller.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>FnbService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
@@ -998,46 +998,46 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>73%</t>
+        <v>86</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>47%</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>fnb</t>
+          <t>queue, maintenance, resources, venue-map, assets, games, rental</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>fnb</t>
+          <t>queue, maintenance, resources, venuemap, assets, games</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>**96 operations and 34 tables — the largest single domain after marketing.** Its own service because a kitchen pass has a latency profile nothing else shares: a bump must land in under a second on a display that may be offline.</t>
+          <t>**Six small domains, 102 operations, one team.** Queue, maintenance, bookable resources, venue mapping, media assets and arcade. None is large enough to deploy alone, all are venue-scoped, none is on the critical sale path, and **all six are licensed as optional modules** — a venue that buys none of them should not be running six idle services.</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
-          <t>Write-heavy during service, idle between. **Two peaks a day, sharply.**</t>
+          <t>Low and steady. Queue readings are the only frequent write.</t>
         </is>
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Down means the kitchen falls back to paper. Offline-capable by design.</t>
+          <t>Down degrades venue operations. Selling and admitting continue.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>FnbService</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
@@ -1046,46 +1046,46 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>fnb</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>fnb</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>**Stock, counting and procurement.** Its own service because `inventory.stock_level` is derived from movements — a rule four operations broke on 20 August — and that derivation is expensive enough to want its own read path.</t>
+          <t>**96 operations and 34 tables — the largest single domain after marketing.** Its own service because a kitchen pass has a latency profile nothing else shares: a bump must land in under a second on a display that may be offline.</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Mixed. Counting is bursty; procurement is not.</t>
+          <t>Write-heavy during service, idle between. **Two peaks a day, sharply.**</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Down blocks receiving and counting; selling continues from the till's cache.</t>
+          <t>Down means the kitchen falls back to paper. Offline-capable by design.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>RetailService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
@@ -1094,328 +1094,376 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>43%</t>
+        <v>18</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>96%</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Merchandise, wallets and gift cards. Modest at 35 operations, and separate because **it is licensed separately** — a venue can run ticketing with no shop.</t>
+          <t>**Stock, counting and procurement.** Its own service because `inventory.stock_level` is derived from movements — a rule four operations broke on 20 August — and that derivation is expensive enough to want its own read path.</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>Follows the sale. Nothing unusual.</t>
+          <t>Mixed. Counting is bursty; procurement is not.</t>
         </is>
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Down means the shop stops; the gates and the restaurant do not.</t>
+          <t>Down blocks receiving and counting; selling continues from the till's cache.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>RetailService</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>retail</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>Merchandise, wallets and gift cards. Modest at 35 operations, and separate because **it is licensed separately** — a venue can run ticketing with no shop.</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Follows the sale. Nothing unusual.</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Down means the shop stops; the gates and the restaurant do not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
           <t>MarketingService</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>engagement</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="C17" s="10" t="n">
+        <v>183</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>marketing-crm</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>**93 operations and 37 tables — the biggest thing in the package, and probably two services eventually.** CRM and campaigns have different write patterns: a guest profile is read constantly and written rarely; a campaign send is a burst of millions of rows nobody reads again.
 **Kept as one for now** because splitting a service before it has a load profile is guessing.</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Bursty on send, read-heavy otherwise. **The one to watch for a split.**</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Down stops campaigns and guest lookup. Neither stops trading.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>AiService</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>engagement</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>ai, qdrant</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>**Separate at any size, and not because of size.** ADR-0020 makes it a hard boundary: only this service writes AI tables, and it is read-only against the transactional core. **That boundary caught four wrongly-placed writes in one week** — it survives because it is enforced, and enforcing it across a shared deployment is harder than across a network.</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>Latency-tolerant, cost-sensitive, token-metered. Different hardware from everything else.</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>Down degrades suggestions and the concierge. **Nothing that takes money depends on it.**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>AiService</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>engagement</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>31</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>ai, qdrant</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>**Separate at any size, and not because of size.** ADR-0020 makes it a hard boundary: only this service writes AI tables, and it is read-only against the transactional core. **That boundary caught four wrongly-placed writes in one week** — it survives because it is enforced, and enforcing it across a shared deployment is harder than across a network.</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Latency-tolerant, cost-sensitive, token-metered. Different hardware from everything else.</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Down degrades suggestions and the concierge. **Nothing that takes money depends on it.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
           <t>PlatformService</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
-        <v>102</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="C19" s="10" t="n">
+        <v>182</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>subscription, platform-ops, public-api</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>**Three contracts, one schema, 41 tables.** Subscription, platform operations and the public API all write `control.*` — **they are one bounded context that was split into three contracts for API-surface reasons, not for data reasons.**
 Splitting them would give three services writing one schema, which is the arrangement every distributed-data guide warns about.</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Low volume, high consequence. Tenant provisioning and licensing.</t>
         </is>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Down blocks provisioning and the developer API. **Trading is unaffected.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>WhiteLabelService</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>white-label</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>whitelabel</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Branding, content, navigation and the tenant's own app configuration. Separate because **it is the only service a tenant edits directly and publishes from** — its deploy cadence follows tenant appetite, not the platform's.</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>Read-heavy and heavily cached. Published, not queried.</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>Down freezes the current published config. Guests see the last good version.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>ReportingService</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
+          <t>WhiteLabelService</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>62%</t>
+        <v>15</v>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>44%</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>white-label</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>whitelabel</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>**Reads almost everything and writes only its own definitions.** Separate because it is the one service that should never touch the transactional primary — ADR-0016 read-write separation exists for this.</t>
+          <t>Branding, content, navigation and the tenant's own app configuration. Separate because **it is the only service a tenant edits directly and publishes from** — its deploy cadence follows tenant appetite, not the platform's.</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Analytical. Runs against the replica and the analytical store.</t>
+          <t>Read-heavy and heavily cached. Published, not queried.</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Down stops dashboards. **Nothing operational depends on it.**</t>
+          <t>Down freezes the current published config. Guests see the last good version.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
+          <t>ReportingService</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>platform</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>reporting</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>**Reads almost everything and writes only its own definitions.** Separate because it is the one service that should never touch the transactional primary — ADR-0016 read-write separation exists for this.</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Analytical. Runs against the replica and the analytical store.</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>Down stops dashboards. **Nothing operational depends on it.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>CrossRegionService</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>platform</t>
         </is>
       </c>
-      <c r="C21" s="10" t="n">
+      <c r="C22" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="D22" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>cross-region</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>sync</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>**The only service that reaches another region** (ADR-0010, ADR-0014). Separate because it is the one place where data crosses a jurisdiction, and **a boundary that matters legally should be a boundary that exists physically.**
 It moves a pseudonymous guest link rather than a guest, which is the whole design.</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>Low volume, high scrutiny.</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J22" s="7" t="inlineStr">
         <is>
           <t>Down blocks cross-region entitlements. Each region continues alone.</t>
         </is>
@@ -1790,9 +1838,9 @@
           <t>postgres</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>games</t>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -2073,7 +2121,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>fnb, orders, resources, retail</t>
+          <t>fnb, orders, resources, wallet</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -2300,21 +2348,21 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>orders, retail</t>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>retail</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>ai, finance</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
@@ -2498,25 +2546,25 @@
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>wallet</t>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr"/>
@@ -2602,7 +2650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3181,21 +3229,21 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>retail.wallet_transaction</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>RetailService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>orders, retail</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -3206,17 +3254,17 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>wallet.wallet_transaction</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
@@ -3231,7 +3279,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>catalogue.product_version</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -3241,11 +3289,11 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>catalogue, fnb</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -3256,23 +3304,48 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>platform.audit_record</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>inventory, tenancy</t>
+          <t>fnb, inventory</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>platform.audit_record</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>TenancyService</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>inventory, tenancy</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
@@ -3391,7 +3464,7 @@
       <c r="A7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>engagement</t>
         </is>
@@ -3411,7 +3484,7 @@
       <c r="A8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>platform</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>platform, workforce, approvals</t>
+          <t>platform, workforce, approvals, accreditation, tenancy</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>queue, maintenance, resources, venuemap, assets, games</t>
+          <t>queue, maintenance, resources, venuemap, assets, games, rental</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>control, subscription</t>
         </is>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C6" s="10" t="n">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>maintenance</t>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
+          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.pos_shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
         </is>
       </c>
     </row>
@@ -2076,16 +2076,16 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>payments</t>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.org_unit` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
+          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.scope` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ai.interaction</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>**First and alone.** Twelve contracts read identity and 289 tables anchor on `platform.org_unit` — a restart here is an outage everywhere.</t>
+          <t>**First and alone.** Twelve contracts read identity and 289 tables anchor on `platform.scope` — a restart here is an outage everywhere.</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3553,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>platform.org_unit is reached by 289 of 379 tables — the tenancy spine. Configuration resolves by walking the path upward until something answers.</t>
+          <t>platform.scope is reached by 289 of 379 tables — the tenancy spine. Configuration resolves by walking the path upward until something answers.</t>
         </is>
       </c>
     </row>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -1480,7 +1480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -2168,16 +2168,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>pricing</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -2186,33 +2186,29 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>nothing writes it</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>ai, marketing-crm, orders</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -2221,24 +2217,24 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>venue-map</t>
+          <t>ai, marketing-crm, orders</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
+          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2247,7 +2243,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -2256,99 +2252,99 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr"/>
+          <t>venue-map</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>ReportingService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>derived, postgres</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>ReportingService</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>derived, postgres</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
+          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>RetailService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -2357,29 +2353,29 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
+          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>RetailService</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
@@ -2392,7 +2388,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2402,23 +2398,23 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
+          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -2427,95 +2423,99 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr"/>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>sync</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>access, games, subscription</t>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>subscription</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>tenancy</t>
+          <t>sync</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>tenancy</t>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>access, games, subscription</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr"/>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>venuemap</t>
+          <t>tenancy</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -2524,116 +2524,147 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>venue-map</t>
+          <t>tenancy</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>access, ai, marketing-crm, workforce</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>venuemap</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>orders, wallet</t>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>venue-map</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>finance</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr"/>
+          <t>access, ai, marketing-crm, workforce</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>whitelabel</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>WhiteLabelService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>white-label</t>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
-        </is>
-      </c>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
+          <t>whitelabel</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>WhiteLabelService</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>white-label</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>TenancyService</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="C37" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr">
         <is>
           <t>Rotas, attendance, announcements, incidents. Small, venue-scoped, and folded into TenancyService because it reads `org_unit` constantly.</t>
         </is>
@@ -2650,7 +2681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3304,17 +3335,17 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>payments.routing_rule</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
@@ -3329,23 +3360,48 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>platform.audit_record</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>inventory, tenancy</t>
+          <t>fnb, inventory</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
         <v>2</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>platform.audit_record</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>TenancyService</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>inventory, tenancy</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -773,12 +773,12 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>catalogue, promotions, seating</t>
+          <t>catalogue, pricing, promotions, seating</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>**What is sold, at what price, in which seat.** Promotions and seating are folded in because both are pricing and availability against the same product — a promotion that cannot see a price list and a seat that cannot see a product are two round trips on the hot path of every sale.</t>
+          <t>**What is sold, at what price, in which seat.** Promotions and seating are folded in because both are pricing and availability against the same product — a promotion that cannot see a price list and a seat that cannot see a product are two round trips on the hot path of every sale. **`pricing` joined it on 20 September**, which closes decision 5 of the schema merge — it took all three `pricing` tables and said the schema needed an owner, and that stayed open because the tables had no operations and a service is inferred from the contract that declares them. The operations were written into `catalogue.yaml`, beside the price lists and products a dynamic rule adjusts: a rule that reads `catalogue.price_list` and `catalogue.product` to compute a price belongs on the side of the boundary those live on, or every evaluation is a cross-service call on the sale path.</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>31</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>nothing writes it</t>
+          <t>catalogue</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>cross-region, orders</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>30</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>55</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>9</v>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>62</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>233</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -828,7 +828,8 @@
         <is>
           <t>**The transactional core.** 96 operations, 34 tables, and the highest write rate in the platform. Separate because its scaling profile is unlike anything else — a Saturday evening is ten times a Tuesday morning.
 **`shift` belongs here and not in Tenancy.** A shift is venue-scoped, which is what made it look like a tenancy concern — but **venue scope is the platform's default rather than a service boundary**: 675 of 1,014 operations are venue-scoped.
-**What decides the service is who owns the tables.** A shift holds cash, `orders.deposit_box` reconciles against payments, and `orders.cash_movement` posts to `ledger.posting` at close. **A till's takings and a till's drawer are the same money counted twice** — separating them makes every settlement a distributed join.</t>
+**What decides the service is who owns the tables.** A shift holds cash, `orders.deposit_box` reconciles against payments, and `orders.cash_movement` posts to `ledger.posting` at close. **A till's takings and a till's drawer are the same money counted twice** — separating them makes every settlement a distributed join.
+**Guest recurring billing lives here, decided by [ADR-0048](../../docs/adr/0048-guest-recurring-billing-is-commerce.md)** rather than in the Control Plane that provisions cells. `payments.dunning_policy` and `payments.dunning_case` are the two newest tables in the service. **A charge on a schedule fails differently from a charge at a till** — nobody is standing at the counter when a renewal declines, so the recovery path is a queue and a timetable rather than a second card.</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
@@ -1866,7 +1867,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>32</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>13</v>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>20</v>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>white-label</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr"/>
@@ -2682,7 +2682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>orders.cart</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>marketing-crm, orders</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -3311,17 +3311,17 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>wallet.wallet_transaction</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
@@ -3336,21 +3336,21 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>catalogue.product_version</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>catalogue, fnb</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -3361,17 +3361,17 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>payments.routing_rule</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
@@ -3386,23 +3386,48 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>platform.audit_record</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>inventory, tenancy</t>
+          <t>fnb, inventory</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>platform.audit_record</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>TenancyService</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>inventory, tenancy</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>81</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>56</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>184</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>44</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>69</v>
@@ -1002,7 +1002,7 @@
         <v>224</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>184</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>52</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -903,46 +903,46 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>61%</t>
+        <v>28</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>**Money, and it is append-only.** 54 operations over 18 tables that are never updated and never deleted — a different discipline from everything around it, and one that should not share a deploy with anything that does mutate.</t>
+          <t>**Eight domains need a wallet and none of them owns it.** A Gold Membership issues F&amp;B credit, parking credits and ride credits into the same wallet, so subscription, games and F&amp;B all read it; `getWalletLiability` aggregates outstanding value across every credit type, so it has to see all of them. The 13 wallet types in the client's library are compositions of owner, credit type and scope rather than thirteen kinds, which is only expressible in one place. **Split out of `retail` on 19 September**, where 13 of retail's 37 operations were the entire wallet runtime while `wallet.yaml` held only its rules.</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Write-heavy, batch-tolerant, not latency-critical. Recognition and revaluation are jobs.</t>
+          <t>Read-heavy on the sale path — every till and reader resolves a balance — and write-heavy on top-up. **Latency-critical in a way LedgerService is not**, which is why the two are separate: the ledger is append-only and batch-tolerant, a balance check is neither.</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>**Correctness over availability.** A ledger that is briefly unavailable is recoverable; one that is briefly wrong is not.</t>
+          <t>**It holds a liability owed to a customer.** A wallet that double-spends is a financial loss, not a bug report. Deduction order across credit lots is FEFO and is decided here, once, rather than per caller.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -951,39 +951,39 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>20</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>61%</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>**Eight domains need a wallet and none of them owns it.** A Gold Membership issues F&amp;B credit, parking credits and ride credits into the same wallet, so subscription, games and F&amp;B all read it; `getWalletLiability` aggregates outstanding value across every credit type, so it has to see all of them. The 13 wallet types in the client's library are compositions of owner, credit type and scope rather than thirteen kinds, which is only expressible in one place. **Split out of `retail` on 19 September**, where 13 of retail's 37 operations were the entire wallet runtime while `wallet.yaml` held only its rules.</t>
+          <t>**Money, and it is append-only.** 54 operations over 18 tables that are never updated and never deleted — a different discipline from everything around it, and one that should not share a deploy with anything that does mutate.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Read-heavy on the sale path — every till and reader resolves a balance — and write-heavy on top-up. **Latency-critical in a way LedgerService is not**, which is why the two are separate: the ledger is append-only and batch-tolerant, a balance check is neither.</t>
+          <t>Write-heavy, batch-tolerant, not latency-critical. Recognition and revaluation are jobs.</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>**It holds a liability owed to a customer.** A wallet that double-spends is a financial loss, not a bug report. Deduction order across credit lots is FEFO and is decided here, once, rather than per caller.</t>
+          <t>**Correctness over availability.** A ledger that is briefly unavailable is recoverable; one that is briefly wrong is not.</t>
         </is>
       </c>
     </row>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>queue, maintenance, resources, venue-map, assets, games, rental</t>
+          <t>queue, maintenance, resources, venue-map, assets, games, rental, transport</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>queue, maintenance, resources, venuemap, assets, games, rental</t>
+          <t>queue, maintenance, resources, venuemap, assets, games, rental, transport</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>64</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1788,16 +1788,16 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>fnb</t>
+          <t>embedded as attributes (jsonb) on orders</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>FnbService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1806,42 +1806,38 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>fnb</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>ai, inventory</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Outlets, menus, kitchen tickets, tables, recipes, food safety. **34 tables and the largest operational domain.** Separate because it is licensed separately and because the kitchen runs offline.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>embedded as window_starts_at and window_ends_at on orders</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>games, wallet</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>orders</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1849,56 +1845,52 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>Arcade, credit ledger, redemption. Fully optional, fully separate.</t>
-        </is>
-      </c>
+      <c r="G13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>identity</t>
+          <t>fnb</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>FnbService</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>postgres, redis</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>identity, orders, public-api, tenancy</t>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>fnb</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>access, approvals, fnb, marketing-crm, reporting, resources +4</t>
+          <t>ai, inventory</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Principals, roles, sessions, credentials. **Read by twelve contracts and reads almost nothing.** Separate because everything resolves a principal before it does anything else, and a schema that everything reads must be one nothing can lock.</t>
+          <t>Outlets, menus, kitchen tickets, tables, recipes, food safety. **34 tables and the largest operational domain.** Separate because it is licensed separately and because the kitchen runs offline.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
@@ -1906,108 +1898,108 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>derived, postgres</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>fnb, inventory, maintenance, retail</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Items, movements, counts, requisitions, purchase orders, suppliers. **The level is derived from the movements** and never stored — a stored level and a movement ledger that disagree is a stock count nobody can reconcile.</t>
+          <t>Arcade, credit ledger, redemption. Fully optional, fully separate.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>identity</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>postgres, redis</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>identity, orders, public-api, tenancy</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory, subscription</t>
+          <t>access, approvals, fnb, marketing-crm, reporting, resources +4</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Journal entries, lines, accounts, settlements. **Append-only, never updated, never deleted.** A different discipline from everything around it, and one that should not share a schema with anything that mutates.</t>
+          <t>Principals, roles, sessions, credentials. **Read by twelve contracts and reads almost nothing.** Separate because everything resolves a principal before it does anything else, and a schema that everything reads must be one nothing can lock.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>derived, postgres</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>fnb, inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>ai, resources</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Assets, work orders, inspections. Separate from `platform.device` because **a turnstile is an asset and a workstation is a station** — one is maintained, the other is configured.</t>
+          <t>Items, movements, counts, requisitions, purchase orders, suppliers. **The level is derived from the movements** and never stored — a stored level and a movement ledger that disagree is a stock count nobody can reconcile.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2016,33 +2008,33 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>access, fnb, identity, marketing-crm, orders, public-api, workforce</t>
+          <t>finance, orders, shift</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>ai, catalogue, promotions, resources, white-label</t>
+          <t>catalogue, inventory, subscription</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Guest profiles, segments, campaigns, consents, cases. **37 tables, the largest single schema.** Holds consent records, which is why it reads `pii` and never writes it.</t>
+          <t>Journal entries, lines, accounts, settlements. **Append-only, never updated, never deleted.** A different discipline from everything around it, and one that should not share a schema with anything that mutates.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2051,33 +2043,33 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, resources, shift, subscription</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>access, catalogue, finance, promotions</t>
+          <t>ai, resources</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.pos_shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
+          <t>Assets, work orders, inspections. Separate from `platform.device` because **a turnstile is an asset and a workstation is a station** — one is maintained, the other is configured.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2086,29 +2078,33 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>access, fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr"/>
+          <t>ai, catalogue, promotions, resources, white-label</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Guest profiles, segments, campaigns, consents, cases. **37 tables, the largest single schema.** Holds consent records, which is why it reads `pii` and never writes it.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>pii</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -2117,33 +2113,33 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>access, identity, marketing-crm</t>
+          <t>fnb, identity, marketing-crm, orders, resources, shift, subscription</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>fnb, orders, resources, wallet</t>
+          <t>access, catalogue, finance, promotions</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Names, phones, emails, documents. **Separate from `identity` deliberately** (ADR-0023): a principal is who may act, a subject is who they are. **One writer only** — which is what makes a subject-access export and a deletion request answerable at all.</t>
+          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.pos_shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -2152,99 +2148,99 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>access, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, platform-ops, shift, subscription, tenancy, white-label</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>ai, public-api, resources, retail, venue-map, workforce</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.scope` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>pricing</t>
+          <t>pii</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>catalogue</t>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>access, identity, marketing-crm</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr"/>
+          <t>fnb, orders, resources, wallet</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Names, phones, emails, documents. **Separate from `identity` deliberately** (ADR-0023): a principal is who may act, a subject is who they are. **One writer only** — which is what makes a subject-access export and a deletion request answerable at all.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>promotions</t>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>access, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, platform-ops, shift, subscription, tenancy, white-label</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>ai, marketing-crm, orders</t>
+          <t>ai, public-api, resources, retail, venue-map, workforce</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
+          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.scope` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>pricing</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -2253,33 +2249,29 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>catalogue</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>venue-map</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
@@ -2288,55 +2280,59 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr"/>
+          <t>ai, marketing-crm, orders</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>ReportingService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>derived, postgres</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>venue-map</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
+          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2345,7 +2341,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -2354,7 +2350,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -2362,34 +2358,30 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
-        </is>
-      </c>
+      <c r="G28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>RetailService</t>
+          <t>ReportingService</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>derived, postgres</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2399,23 +2391,23 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
+          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -2424,33 +2416,33 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
+          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>RetailService</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -2459,64 +2451,68 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>white-label</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr"/>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>sync</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>access, games, subscription</t>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>seating</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>cross-region, orders</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
+          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>tenancy</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -2525,12 +2521,12 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>tenancy</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>white-label</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
@@ -2538,65 +2534,65 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>venuemap</t>
+          <t>sync</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>venue-map</t>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>access, games, subscription</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>access, ai, marketing-crm, workforce</t>
+          <t>cross-region, orders</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>tenancy</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>orders, wallet</t>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>tenancy</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
@@ -2604,16 +2600,16 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>whitelabel</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>WhiteLabelService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
@@ -2622,50 +2618,147 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>white-label</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>venuemap</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>VenueOpsService</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>venue-map</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>access, ai, marketing-crm, workforce</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>wallet</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>WalletService</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>whitelabel</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>WhiteLabelService</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>white-label</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>TenancyService</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C40" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>Rotas, attendance, announcements, incidents. Small, venue-scoped, and folded into TenancyService because it reads `org_unit` constantly.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>415</v>
+        <v>444</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>cross-region, identity, marketing-crm, subscription, tenancy, venue-map +1</t>
+          <t>cross-region, identity, marketing-crm, reporting, subscription, tenancy +2</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>marketing-crm, platform-ops, public-api, subscription, white-label</t>
+          <t>approvals, marketing-crm, platform-ops, public-api, subscription, white-label</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory, subscription</t>
+          <t>catalogue, inventory, payments, subscription</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>access, fnb, identity, marketing-crm, orders, public-api, workforce</t>
+          <t>access, approvals, fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>access, catalogue, finance, promotions</t>
+          <t>access, catalogue, finance, payments, promotions</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>finance, orders, payments</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -2271,21 +2271,21 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>promotions</t>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>orders, promotions</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>ai, marketing-crm, orders</t>
+          <t>ai, marketing-crm</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>access, ai, marketing-crm, workforce</t>
+          <t>access, ai, marketing-crm, resources, workforce</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, marketing-crm</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2843,7 +2843,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3054,71 +3054,71 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>inventory.movement</t>
+          <t>marketing.consent_record</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>fnb, inventory, retail</t>
+          <t>access, marketing-crm, orders</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>approvals.request</t>
+          <t>inventory.movement</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription, workforce</t>
+          <t>fnb, inventory, retail</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>marketing.consent_record</t>
+          <t>approvals.request</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>access, marketing-crm, orders</t>
+          <t>approvals, subscription, workforce</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>catalogue.product</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3164,11 +3164,11 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>catalogue, fnb, inventory</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>catalogue.inventory_hold</t>
+          <t>catalogue.product</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -3189,11 +3189,11 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>catalogue, orders</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -3204,21 +3204,21 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>platform.region_settings</t>
+          <t>catalogue.inventory_hold</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>finance, tenancy</t>
+          <t>catalogue, orders</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>orders.payment</t>
+          <t>platform.region_settings</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>orders, subscription</t>
+          <t>finance, tenancy</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>platform.dsar_request</t>
+          <t>orders.payment</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>cross-region, identity</t>
+          <t>orders, subscription</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -3279,46 +3279,46 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>pii.subject</t>
+          <t>promotions.promotion_evaluation_trace</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>orders, promotions</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>platform.dsar_request</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>cross-region, identity</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -3329,46 +3329,46 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ai.activity</t>
+          <t>pii.subject</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>identity, marketing-crm</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>orders.cart</t>
+          <t>maintenance.asset</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>marketing-crm, orders</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -3404,46 +3404,46 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -3454,21 +3454,21 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>control.partner_agreement</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
@@ -3479,21 +3479,21 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>control.partner_application</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -3504,23 +3504,173 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>platform.audit_record</t>
+          <t>control.partner_change_request</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>inventory, tenancy</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
         <v>2</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>marketing.privacy_notice_governance</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>MarketingService</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>approvals, marketing-crm</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>orders.cart</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>OrderService</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>marketing-crm, orders</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>wallet.wallet_transaction</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>WalletService</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>catalogue.product_version</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>CatalogueService</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>catalogue, fnb</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>payments.routing_rule</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>OrderService</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>orders, payments</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>platform.audit_record</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>TenancyService</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>inventory, tenancy</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -903,46 +903,46 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>27</v>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>61%</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>**Eight domains need a wallet and none of them owns it.** A Gold Membership issues F&amp;B credit, parking credits and ride credits into the same wallet, so subscription, games and F&amp;B all read it; `getWalletLiability` aggregates outstanding value across every credit type, so it has to see all of them. The 13 wallet types in the client's library are compositions of owner, credit type and scope rather than thirteen kinds, which is only expressible in one place. **Split out of `retail` on 19 September**, where 13 of retail's 37 operations were the entire wallet runtime while `wallet.yaml` held only its rules.</t>
+          <t>**Money, and it is append-only.** 54 operations over 18 tables that are never updated and never deleted — a different discipline from everything around it, and one that should not share a deploy with anything that does mutate.</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>Read-heavy on the sale path — every till and reader resolves a balance — and write-heavy on top-up. **Latency-critical in a way LedgerService is not**, which is why the two are separate: the ledger is append-only and batch-tolerant, a balance check is neither.</t>
+          <t>Write-heavy, batch-tolerant, not latency-critical. Recognition and revaluation are jobs.</t>
         </is>
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>**It holds a liability owed to a customer.** A wallet that double-spends is a financial loss, not a bug report. Deduction order across credit lots is FEFO and is decided here, once, rather than per caller.</t>
+          <t>**Correctness over availability.** A ledger that is briefly unavailable is recoverable; one that is briefly wrong is not.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -951,39 +951,39 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>61%</t>
+        <v>31</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>**Money, and it is append-only.** 54 operations over 18 tables that are never updated and never deleted — a different discipline from everything around it, and one that should not share a deploy with anything that does mutate.</t>
+          <t>**Eight domains need a wallet and none of them owns it.** A Gold Membership issues F&amp;B credit, parking credits and ride credits into the same wallet, so subscription, games and F&amp;B all read it; `getWalletLiability` aggregates outstanding value across every credit type, so it has to see all of them. The 13 wallet types in the client's library are compositions of owner, credit type and scope rather than thirteen kinds, which is only expressible in one place. **Split out of `retail` on 19 September**, where 13 of retail's 37 operations were the entire wallet runtime while `wallet.yaml` held only its rules.</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Write-heavy, batch-tolerant, not latency-critical. Recognition and revaluation are jobs.</t>
+          <t>Read-heavy on the sale path — every till and reader resolves a balance — and write-heavy on top-up. **Latency-critical in a way LedgerService is not**, which is why the two are separate: the ledger is append-only and batch-tolerant, a balance check is neither.</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>**Correctness over availability.** A ledger that is briefly unavailable is recoverable; one that is briefly wrong is not.</t>
+          <t>**It holds a liability owed to a customer.** A wallet that double-spends is a financial loss, not a bug report. Deduction order across credit lots is FEFO and is decided here, once, rather than per caller.</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>49</v>
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>24</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr"/>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>ai, maintenance, seating, venue-map</t>
+          <t>ai, identity, maintenance, seating, tenancy, venue-map</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm, platform-ops, public-api, subscription, white-label</t>
+          <t>approvals, finance, marketing-crm, platform-ops, public-api, subscription, white-label</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>ai, finance</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -1929,7 +1929,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>ai, catalogue, promotions, resources, white-label</t>
+          <t>ai, catalogue, promotions, queue, resources, white-label</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, resources, shift, subscription</t>
+          <t>fnb, identity, marketing-crm, orders, payments, resources, shift, subscription, wallet</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>access, catalogue, finance, payments, promotions</t>
+          <t>access, ai, catalogue, finance, promotions</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>access, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, platform-ops, shift, subscription, tenancy, white-label</t>
+          <t>access, accreditation, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>ai, marketing-crm</t>
+          <t>ai, marketing-crm, queue</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>venue-map</t>
+          <t>ai, venue-map</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>access, marketing-crm</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>identity</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2839,11 +2839,11 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>access, approvals, catalogue, finance, fnb, inventory, maintenance, marketing-crm, orders, platform-ops, shift, subscription, white-label</t>
+          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
@@ -2879,32 +2879,32 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>access.entitlement</t>
+          <t>platform.audit_record</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>AccessService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>access, catalogue, orders</t>
+          <t>finance, inventory, orders, payments, tenancy</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>orders.order_line</t>
+          <t>orders.payment</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2914,11 +2914,11 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>fnb, orders, subscription</t>
+          <t>orders, payments, subscription, wallet</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -2929,146 +2929,146 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>orders.sales_order</t>
+          <t>access.entitlement</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>AccessService</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>identity, orders, subscription</t>
+          <t>access, catalogue, orders</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
+          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>ledger.journal_entry</t>
+          <t>orders.order_line</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>fnb, orders, subscription</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>As above. The journal is written by whatever caused the money to move.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ledger.posting</t>
+          <t>orders.sales_order</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>identity, orders, subscription</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>**A till closing is a ledger act.** Settling a shift posts to the ledger, and a payment writes its own entry — appending, never redefining.</t>
+          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>sync.rejection</t>
+          <t>ledger.journal_entry</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>access, games, subscription</t>
+          <t>finance, orders, shift</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>As above. The journal is written by whatever caused the money to move.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>identity.delegated_access</t>
+          <t>ledger.posting</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>identity, orders, public-api</t>
+          <t>finance, orders, shift</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
+          <t>**A till closing is a ledger act.** Settling a shift posts to the ledger, and a payment writes its own entry — appending, never redefining.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>marketing.consent_record</t>
+          <t>sync.rejection</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>access, marketing-crm, orders</t>
+          <t>access, games, subscription</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -3079,46 +3079,46 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>inventory.movement</t>
+          <t>identity.delegated_access</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory, retail</t>
+          <t>identity, orders, public-api</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
+          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>approvals.request</t>
+          <t>marketing.consent_record</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription, workforce</t>
+          <t>access, marketing-crm, orders</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -3129,46 +3129,46 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>orders.stored_value_authorisation</t>
+          <t>inventory.movement</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>marketing-crm, orders, resources</t>
+          <t>fnb, inventory, retail</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>approvals.request</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>catalogue, fnb, inventory</t>
+          <t>approvals, subscription, workforce</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
@@ -3179,21 +3179,21 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>catalogue.product</t>
+          <t>orders.stored_value_authorisation</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>marketing-crm, orders, resources</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>catalogue.inventory_hold</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -3214,11 +3214,11 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>catalogue, orders</t>
+          <t>catalogue, fnb, inventory</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
@@ -3229,21 +3229,21 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>platform.region_settings</t>
+          <t>catalogue.product</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>finance, tenancy</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -3254,21 +3254,21 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>orders.payment</t>
+          <t>catalogue.inventory_hold</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>orders, subscription</t>
+          <t>catalogue, orders</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -3279,21 +3279,21 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>promotions.promotion_evaluation_trace</t>
+          <t>platform.region_settings</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>orders, promotions</t>
+          <t>finance, tenancy</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -3304,21 +3304,21 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>platform.dsar_request</t>
+          <t>promotions.promotion_evaluation_trace</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>cross-region, identity</t>
+          <t>orders, promotions</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -3329,46 +3329,46 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>pii.subject</t>
+          <t>orders.refund</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>platform.dsar_request</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>cross-region, identity</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -3379,71 +3379,71 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>maintenance.asset</t>
+          <t>pii.subject</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>identity, marketing-crm</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>ai.activity</t>
+          <t>ledger.journal_line</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>finance, orders</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>control.invoice_line</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>finance, subscription</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -3454,17 +3454,17 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>control.partner_agreement</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
@@ -3479,21 +3479,21 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>control.partner_application</t>
+          <t>maintenance.asset</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -3504,46 +3504,46 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>control.partner_change_request</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>marketing.privacy_notice_governance</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -3554,17 +3554,17 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>orders.cart</t>
+          <t>control.partner_agreement</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>marketing-crm, orders</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
@@ -3579,21 +3579,21 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>control.partner_application</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -3604,21 +3604,21 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>control.partner_change_request</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -3629,17 +3629,17 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>marketing.privacy_notice_governance</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>approvals, marketing-crm</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
@@ -3654,23 +3654,98 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>platform.audit_record</t>
+          <t>orders.cart</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>inventory, tenancy</t>
+          <t>marketing-crm, orders</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>wallet.wallet_transaction</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>WalletService</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>catalogue.product_version</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>CatalogueService</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>catalogue, fnb</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>payments.routing_rule</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>OrderService</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>orders, payments</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>134</v>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>76</v>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>27</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>31</v>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>120</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>22</v>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>catalogue, fnb, inventory, orders</t>
+          <t>catalogue, fnb, inventory, orders, payments, venue-map</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>approvals, finance, marketing-crm, platform-ops, public-api, subscription, white-label</t>
+          <t>approvals, finance, marketing-crm, platform-ops, public-api, subscription, tenancy, white-label</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1788,16 +1788,16 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>embedded as attributes (jsonb) on orders</t>
+          <t>fnb</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FnbService</t>
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1806,200 +1806,208 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>fnb</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr"/>
+          <t>ai, inventory, promotions</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Outlets, menus, kitchen tickets, tables, recipes, food safety. **34 tables and the largest operational domain.** Separate because it is licensed separately and because the kitchen runs offline.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>embedded as window_starts_at and window_ends_at on orders</t>
+          <t>games</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
+          <t>VenueOpsService</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>games, wallet</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>orders</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Arcade, credit ledger, redemption. Fully optional, fully separate.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>fnb</t>
+          <t>identity</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>FnbService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>fnb</t>
+          <t>postgres, redis</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>identity, orders, public-api, tenancy</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>ai, inventory</t>
+          <t>access, approvals, fnb, marketing-crm, reporting, resources +4</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Outlets, menus, kitchen tickets, tables, recipes, food safety. **34 tables and the largest operational domain.** Separate because it is licensed separately and because the kitchen runs offline.</t>
+          <t>Principals, roles, sessions, credentials. **Read by twelve contracts and reads almost nothing.** Separate because everything resolves a principal before it does anything else, and a schema that everything reads must be one nothing can lock.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>derived, postgres</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>fnb, inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Arcade, credit ledger, redemption. Fully optional, fully separate.</t>
+          <t>Items, movements, counts, requisitions, purchase orders, suppliers. **The level is derived from the movements** and never stored — a stored level and a movement ledger that disagree is a stock count nobody can reconcile.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>identity</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>postgres, redis</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>identity, orders, public-api, tenancy</t>
+          <t>finance, orders, payments, shift</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>access, approvals, fnb, marketing-crm, reporting, resources +4</t>
+          <t>catalogue, inventory, subscription</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Principals, roles, sessions, credentials. **Read by twelve contracts and reads almost nothing.** Separate because everything resolves a principal before it does anything else, and a schema that everything reads must be one nothing can lock.</t>
+          <t>Journal entries, lines, accounts, settlements. **Append-only, never updated, never deleted.** A different discipline from everything around it, and one that should not share a schema with anything that mutates.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>derived, postgres</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>fnb, inventory, maintenance, retail</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>ai, resources</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Items, movements, counts, requisitions, purchase orders, suppliers. **The level is derived from the movements** and never stored — a stored level and a movement ledger that disagree is a stock count nobody can reconcile.</t>
+          <t>Assets, work orders, inspections. Separate from `platform.device` because **a turnstile is an asset and a workstation is a station** — one is maintained, the other is configured.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2008,33 +2016,33 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>access, approvals, fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory, payments, subscription</t>
+          <t>ai, catalogue, promotions, queue, resources, white-label</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Journal entries, lines, accounts, settlements. **Append-only, never updated, never deleted.** A different discipline from everything around it, and one that should not share a schema with anything that mutates.</t>
+          <t>Guest profiles, segments, campaigns, consents, cases. **37 tables, the largest single schema.** Holds consent records, which is why it reads `pii` and never writes it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2043,33 +2051,33 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>fnb, identity, marketing-crm, orders, payments, resources, shift, subscription, venue-map, wallet</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>ai, resources</t>
+          <t>access, ai, catalogue, finance, promotions</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Assets, work orders, inspections. Separate from `platform.device` because **a turnstile is an asset and a workstation is a station** — one is maintained, the other is configured.</t>
+          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.pos_shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2078,33 +2086,29 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>access, approvals, fnb, identity, marketing-crm, orders, public-api, workforce</t>
+          <t>finance, orders, payments</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>ai, catalogue, promotions, queue, resources, white-label</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>Guest profiles, segments, campaigns, consents, cases. **37 tables, the largest single schema.** Holds consent records, which is why it reads `pii` and never writes it.</t>
-        </is>
-      </c>
+          <t>wallet</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>pii</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -2113,33 +2117,33 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, payments, resources, shift, subscription, wallet</t>
+          <t>access, identity, marketing-crm</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>access, ai, catalogue, finance, promotions</t>
+          <t>fnb, orders, resources, wallet</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.pos_shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
+          <t>Names, phones, emails, documents. **Separate from `identity` deliberately** (ADR-0023): a principal is who may act, a subject is who they are. **One writer only** — which is what makes a subject-access export and a deletion request answerable at all.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -2148,64 +2152,64 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>finance, orders, payments</t>
+          <t>access, accreditation, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>wallet</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr"/>
+          <t>ai, public-api, retail, venue-map, workforce</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.scope` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>pii</t>
+          <t>pricing</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>access, identity, marketing-crm</t>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>catalogue</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>fnb, orders, resources, wallet</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>Names, phones, emails, documents. **Separate from `identity` deliberately** (ADR-0023): a principal is who may act, a subject is who they are. **One writer only** — which is what makes a subject-access export and a deletion request answerable at all.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
@@ -2214,33 +2218,33 @@
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>orders, promotions</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>ai, public-api, resources, retail, venue-map, workforce</t>
+          <t>ai, marketing-crm, queue, venue-map</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.scope` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
+          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>pricing</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -2249,90 +2253,90 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>catalogue</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr"/>
+          <t>ai, venue-map</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>orders, promotions</t>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>rental</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>ai, marketing-crm, queue</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>ReportingService</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>derived, postgres</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ai, venue-map</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
+          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -2341,7 +2345,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -2350,38 +2354,42 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr"/>
+          <t>maintenance</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>ReportingService</t>
+          <t>RetailService</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>derived, postgres</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2391,23 +2399,23 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
+          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -2416,33 +2424,33 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
+          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>RetailService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -2451,68 +2459,64 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
-        </is>
-      </c>
+          <t>white-label</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>sync</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>seating</t>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>access, games, orders, subscription</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>cross-region</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
+          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>tenancy</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -2521,12 +2525,12 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>tenancy</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>white-label</t>
+          <t>access, marketing-crm</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
@@ -2534,47 +2538,43 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>sync</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
-        <is>
-          <t>access, games, subscription</t>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>transport</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>cross-region, orders</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>tenancy</t>
+          <t>venuemap</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
@@ -2587,43 +2587,47 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>tenancy</t>
+          <t>venue-map</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>access, marketing-crm</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
+          <t>access, ai, marketing-crm, resources, workforce</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>transport</t>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr"/>
@@ -2631,16 +2635,16 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>venuemap</t>
+          <t>whitelabel</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>WhiteLabelService</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -2649,116 +2653,50 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>venue-map</t>
+          <t>white-label</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>access, ai, marketing-crm, resources, workforce</t>
+          <t>ai, catalogue, marketing-crm</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>workforce</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>orders, wallet</t>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>workforce</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>finance</t>
-        </is>
-      </c>
-      <c r="G38" s="10" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>whitelabel</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>WhiteLabelService</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>white-label</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>ai, marketing-crm</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>workforce</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>TenancyService</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>workforce</t>
-        </is>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
+          <t>identity, maintenance</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>Rotas, attendance, announcements, incidents. Small, venue-scoped, and folded into TenancyService because it reads `org_unit` constantly.</t>
         </is>
@@ -2775,7 +2713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2843,7 +2781,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -2854,71 +2792,71 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>marketing.message_dispatch</t>
+          <t>platform.idempotency_record</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, public-api, workforce</t>
+          <t>access, finance, fnb, marketing-crm, orders, payments, wallet</t>
         </is>
       </c>
       <c r="D6" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>**Five writers, and every one is sending a message somebody asked for.** A verification email, a payment link, an evacuation notice.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>platform.audit_record</t>
+          <t>marketing.message_dispatch</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>finance, inventory, orders, payments, tenancy</t>
+          <t>fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**Five writers, and every one is sending a message somebody asked for.** A verification email, a payment link, an evacuation notice.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>orders.payment</t>
+          <t>platform.audit_record</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>orders, payments, subscription, wallet</t>
+          <t>finance, inventory, orders, payments, tenancy</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
@@ -2929,17 +2867,17 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>access.entitlement</t>
+          <t>catalogue.inventory_hold</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>AccessService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>access, catalogue, orders</t>
+          <t>catalogue, orders, payments, venue-map</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
@@ -2947,14 +2885,14 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>orders.order_line</t>
+          <t>orders.payment</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -2964,11 +2902,11 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>fnb, orders, subscription</t>
+          <t>orders, payments, subscription, wallet</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -2979,96 +2917,96 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>orders.sales_order</t>
+          <t>ledger.journal_entry</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>identity, orders, subscription</t>
+          <t>finance, orders, payments, shift</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
+          <t>As above. The journal is written by whatever caused the money to move.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>ledger.journal_entry</t>
+          <t>sync.rejection</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>access, games, orders, subscription</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>As above. The journal is written by whatever caused the money to move.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ledger.posting</t>
+          <t>inventory.movement</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>fnb, inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>**A till closing is a ledger act.** Settling a shift posts to the ledger, and a payment writes its own entry — appending, never redefining.</t>
+          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>sync.rejection</t>
+          <t>catalogue.channel_capacity</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>access, games, subscription</t>
+          <t>catalogue, orders, payments</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -3079,46 +3017,46 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>identity.delegated_access</t>
+          <t>access.entitlement</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>AccessService</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>identity, orders, public-api</t>
+          <t>access, catalogue, orders</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
+          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>marketing.consent_record</t>
+          <t>orders.order_line</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>access, marketing-crm, orders</t>
+          <t>fnb, orders, subscription</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -3129,71 +3067,71 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>inventory.movement</t>
+          <t>orders.sales_order</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory, retail</t>
+          <t>identity, orders, subscription</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
+          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>approvals.request</t>
+          <t>ledger.posting</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription, workforce</t>
+          <t>finance, orders, shift</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**A till closing is a ledger act.** Settling a shift posts to the ledger, and a payment writes its own entry — appending, never redefining.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>orders.stored_value_authorisation</t>
+          <t>ledger.journal_line</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>marketing-crm, orders, resources</t>
+          <t>finance, orders, payments</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -3204,46 +3142,46 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>identity.delegated_access</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>catalogue, fnb, inventory</t>
+          <t>identity, orders, public-api</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>catalogue.product</t>
+          <t>marketing.consent_record</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>access, marketing-crm, orders</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -3254,21 +3192,21 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>catalogue.inventory_hold</t>
+          <t>approvals.request</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>catalogue, orders</t>
+          <t>approvals, subscription, workforce</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -3279,21 +3217,21 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>platform.region_settings</t>
+          <t>orders.cart</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>finance, tenancy</t>
+          <t>marketing-crm, orders, venue-map</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -3304,21 +3242,21 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>promotions.promotion_evaluation_trace</t>
+          <t>orders.stored_value_authorisation</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>orders, promotions</t>
+          <t>marketing-crm, orders, resources</t>
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -3329,21 +3267,21 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>orders.refund</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>catalogue, fnb, inventory</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -3354,21 +3292,21 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>platform.dsar_request</t>
+          <t>catalogue.product</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>cross-region, identity</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -3379,46 +3317,46 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>pii.subject</t>
+          <t>platform.region_settings</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>finance, tenancy</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>ledger.journal_line</t>
+          <t>orders.order_event</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>finance, orders</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -3429,17 +3367,17 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>control.invoice_line</t>
+          <t>promotions.promotion_evaluation_trace</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>finance, subscription</t>
+          <t>orders, promotions</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
@@ -3454,21 +3392,21 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>orders.refund</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
@@ -3479,21 +3417,21 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>maintenance.asset</t>
+          <t>payments.payment_attempt</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -3504,46 +3442,46 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>ai.activity</t>
+          <t>ledger.price_variance</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>finance, orders</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>platform.dsar_request</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>cross-region, identity</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -3554,32 +3492,32 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>control.partner_agreement</t>
+          <t>pii.subject</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>identity, marketing-crm</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>control.partner_application</t>
+          <t>control.invoice_line</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -3589,7 +3527,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>finance, subscription</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
@@ -3604,21 +3542,21 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>control.partner_change_request</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -3629,21 +3567,21 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>marketing.privacy_notice_governance</t>
+          <t>maintenance.asset</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -3654,21 +3592,21 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>orders.cart</t>
+          <t>inventory.stock_reservation</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>marketing-crm, orders</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -3679,46 +3617,46 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
@@ -3729,23 +3667,198 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>control.partner_agreement</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>PlatformService</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>approvals, subscription</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>control.partner_application</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>PlatformService</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>approvals, subscription</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>control.partner_change_request</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>PlatformService</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>approvals, subscription</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>marketing.privacy_notice_governance</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>MarketingService</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>approvals, marketing-crm</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>orders.cart_line</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>OrderService</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>orders, venue-map</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>wallet.wallet_transaction</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>WalletService</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>catalogue.product_version</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>CatalogueService</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>catalogue, fnb</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
           <t>payments.routing_rule</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>OrderService</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>orders, payments</t>
         </is>
       </c>
-      <c r="D41" s="7" t="n">
+      <c r="D48" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E48" s="10" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -1291,7 +1291,7 @@
         <v>212</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1928,51 +1928,47 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>ledger</t>
+          <t>kernel</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>finance, orders, payments, shift</t>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>nothing writes it</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory, subscription</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>Journal entries, lines, accounts, settlements. **Append-only, never updated, never deleted.** A different discipline from everything around it, and one that should not share a schema with anything that mutates.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>ledger</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
@@ -1981,33 +1977,33 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>finance, orders, payments, shift</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>ai, resources</t>
+          <t>catalogue, inventory, subscription</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Assets, work orders, inspections. Separate from `platform.device` because **a turnstile is an asset and a workstation is a station** — one is maintained, the other is configured.</t>
+          <t>Journal entries, lines, accounts, settlements. **Append-only, never updated, never deleted.** A different discipline from everything around it, and one that should not share a schema with anything that mutates.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>marketing</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2016,33 +2012,33 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>access, approvals, fnb, identity, marketing-crm, orders, public-api, workforce</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>ai, catalogue, promotions, queue, resources, white-label</t>
+          <t>ai, resources</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Guest profiles, segments, campaigns, consents, cases. **37 tables, the largest single schema.** Holds consent records, which is why it reads `pii` and never writes it.</t>
+          <t>Assets, work orders, inspections. Separate from `platform.device` because **a turnstile is an asset and a workstation is a station** — one is maintained, the other is configured.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>orders</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2051,24 +2047,24 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, payments, resources, shift, subscription, venue-map, wallet</t>
+          <t>access, approvals, fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>access, ai, catalogue, finance, promotions</t>
+          <t>ai, catalogue, promotions, queue, resources, white-label</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.pos_shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
+          <t>Guest profiles, segments, campaigns, consents, cases. **37 tables, the largest single schema.** Holds consent records, which is why it reads `pii` and never writes it.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>orders</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -2077,7 +2073,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2086,29 +2082,33 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>finance, orders, payments</t>
+          <t>fnb, identity, marketing-crm, orders, payments, resources, shift, subscription, venue-map, wallet</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>wallet</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr"/>
+          <t>access, ai, catalogue, finance, promotions</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Carts, orders, lines, payments, refunds, shifts, cash. **The transactional core and the highest write rate in the platform.** Also holds `orders.pos_shift` and the cash tables — a till session is an order-side artefact, not a workforce one.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>pii</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
@@ -2117,33 +2117,29 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>access, identity, marketing-crm</t>
+          <t>finance, orders, payments</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>fnb, orders, resources, wallet</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Names, phones, emails, documents. **Separate from `identity` deliberately** (ADR-0023): a principal is who may act, a subject is who they are. **One writer only** — which is what makes a subject-access export and a deletion request answerable at all.</t>
-        </is>
-      </c>
+          <t>wallet</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>pii</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -2152,55 +2148,59 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, identity, marketing-crm</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>ai, public-api, retail, venue-map, workforce</t>
+          <t>fnb, orders, resources, wallet</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.scope` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
+          <t>Names, phones, emails, documents. **Separate from `identity` deliberately** (ADR-0023): a principal is who may act, a subject is who they are. **One writer only** — which is what makes a subject-access export and a deletion request answerable at all.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>pricing</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>catalogue</t>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>access, accreditation, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr"/>
+          <t>ai, public-api, retail, venue-map, workforce</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Tenants, venues, workstations, devices, scope nodes. **`platform.scope` is reached by 289 of 379 tables** — the tenancy spine, and the terminal anchor for almost everything in the package.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>promotions</t>
+          <t>pricing</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -2209,68 +2209,64 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>orders, promotions</t>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>catalogue</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>ai, marketing-crm, queue, venue-map</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>queue</t>
+          <t>promotions</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>queue</t>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>orders, promotions</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>ai, venue-map</t>
+          <t>ai, marketing-crm, queue, venue-map</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
+          <t>Promotions, bundles, coupons, vouchers. Separate because **a promotion is evaluated on the hot path of every sale** and versioned independently of price.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -2279,7 +2275,7 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
@@ -2288,25 +2284,29 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>rental</t>
+          <t>queue</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr"/>
+          <t>ai, venue-map</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Queues, entries, wait readings. Adaptor-first (ADR-0012) — the schema holds what a third-party queue system reports.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>ReportingService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
@@ -2314,73 +2314,69 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>derived, postgres</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>reporting</t>
+          <t>rental</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>ReportingService</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>derived, postgres</t>
         </is>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>reporting</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>maintenance</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
+          <t>Report definitions, schedules, executions, dashboards. **Reads almost everything and writes only its own definitions** — the schema that must never touch the transactional primary.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>RetailService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -2389,33 +2385,33 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>retail</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>maintenance</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
+          <t>Bookable objects — cabanas, equipment, instructors. **A locker is a resource, not an entitlement**, because it is checked out and returned.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>RetailService</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
@@ -2424,7 +2420,7 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>seating</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -2434,23 +2430,23 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
+          <t>Merchandise, wallets, gift cards, retail sales. Separate because **a venue can run ticketing with no shop** — the schema exists or it does not, per licence.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
@@ -2459,95 +2455,99 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>subscription</t>
+          <t>seating</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>white-label</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr"/>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Seat maps, zones, categories, holds. Separate from `catalogue` because a seat map outlives the performances sold against it.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>sync</t>
+          <t>subscription</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>access, games, orders, subscription</t>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>subscription</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>cross-region</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
-        </is>
-      </c>
+          <t>white-label</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>tenancy</t>
+          <t>sync</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>tenancy</t>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>access, games, orders, subscription</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>access, marketing-crm</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr"/>
+          <t>cross-region</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Cross-cell links and rejections. **The only schema that reaches another region** — a boundary that matters legally, made a boundary that exists physically.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>tenancy</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>transport</t>
+          <t>tenancy</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>access, marketing-crm</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr"/>
@@ -2569,7 +2569,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>venuemap</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
@@ -2587,116 +2587,147 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>venue-map</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>access, ai, marketing-crm, resources, workforce</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>wallet</t>
+          <t>venuemap</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>orders, wallet</t>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>venue-map</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>finance</t>
-        </is>
-      </c>
-      <c r="G36" s="10" t="inlineStr"/>
+          <t>access, ai, marketing-crm, resources, workforce</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Points, walkways, geometry. Separate because a venue map is imported and labelled as a pipeline, not edited as a record.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>whitelabel</t>
+          <t>wallet</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>WhiteLabelService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>white-label</t>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>ai, catalogue, marketing-crm</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
-        </is>
-      </c>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
+          <t>whitelabel</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>WhiteLabelService</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>white-label</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>ai, catalogue, marketing-crm</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Brand identity, content pages, navigation, config versions. **The only schema a tenant edits directly and publishes from.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>TenancyService</t>
         </is>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C39" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>postgres</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>workforce</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>identity, maintenance</t>
         </is>
       </c>
-      <c r="G38" s="10" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>Rotas, attendance, announcements, incidents. Small, venue-scoped, and folded into TenancyService because it reads `org_unit` constantly.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -2883,11 +2883,11 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>finance, inventory, orders, payments, tenancy</t>
+          <t>finance, inventory, orders, payments, platform-ops, tenancy</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>108</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>38</v>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>31</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>114</v>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>51</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>132</v>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>platform, workforce, approvals, accreditation, tenancy</t>
+          <t>platform, workforce, approvals, accreditation, tenancy, kernel</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>137</v>
@@ -807,7 +807,7 @@
         <v>298</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>77</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>124</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>132</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>108</v>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>access, ai, finance, games, marketing-crm, promotions +3</t>
+          <t>access, ai, finance, games, marketing-crm, promotions +4</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C16" s="10" t="n">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2453,9 +2453,9 @@
           <t>postgres</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>seating</t>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2554,14 +2554,14 @@
           <t>postgres</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>tenancy</t>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>access, tenancy</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>access, marketing-crm</t>
+          <t>marketing-crm</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="D24" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -3573,17 +3573,17 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>seating.seat_hold</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
@@ -3598,21 +3598,21 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>maintenance.asset</t>
+          <t>inventory.count_line</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>fnb, inventory</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>inventory.stock_reservation</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -3648,46 +3648,46 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>ai.activity</t>
+          <t>maintenance.asset</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>inventory.stock_reservation</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
@@ -3698,46 +3698,46 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>control.partner_agreement</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>control.partner_application</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>control.partner_change_request</t>
+          <t>control.partner_agreement</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -3773,21 +3773,21 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>marketing.privacy_notice_governance</t>
+          <t>control.partner_application</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>orders.cart_line</t>
+          <t>control.partner_change_request</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>orders, venue-map</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>marketing.privacy_notice_governance</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>approvals, marketing-crm</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
@@ -3848,21 +3848,21 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>orders.cart_line</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>orders, venue-map</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3873,23 +3873,123 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
+          <t>wallet.wallet_transaction</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>WalletService</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>orders, wallet</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>catalogue.product_version</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>CatalogueService</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>catalogue, fnb</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
           <t>payments.routing_rule</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>OrderService</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
         <is>
           <t>orders, payments</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D50" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="10" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>seating.seat_hold_item</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>CatalogueService</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>catalogue, seating</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>tenancy.data_retention_setting</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>TenancyService</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>access, tenancy</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>109</v>
@@ -711,7 +711,7 @@
         <v>94</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>77</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>132</v>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>identity, orders, public-api, tenancy</t>
+          <t>identity, orders, tenancy</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -3173,17 +3173,17 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>identity.delegated_access</t>
+          <t>marketing.consent_record</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>identity, orders, public-api</t>
+          <t>access, marketing-crm, orders</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
@@ -3191,28 +3191,28 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>marketing.consent_record</t>
+          <t>inventory.stock_reservation</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>access, marketing-crm, orders</t>
+          <t>inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>pii.subject</t>
+          <t>identity.role_permission</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -3533,82 +3533,82 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>identity, tenancy</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>control.invoice_line</t>
+          <t>identity.delegated_access</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>finance, subscription</t>
+          <t>identity, orders</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>seating.seat_hold</t>
+          <t>pii.subject</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>catalogue, seating</t>
+          <t>identity, marketing-crm</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>inventory.count_line</t>
+          <t>control.invoice_line</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>finance, subscription</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
@@ -3623,17 +3623,17 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>seating.seat_hold</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
@@ -3648,17 +3648,17 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>maintenance.asset</t>
+          <t>inventory.count_line</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>fnb, inventory</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
@@ -3673,7 +3673,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>inventory.stock_reservation</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
@@ -3698,32 +3698,32 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>ai.activity</t>
+          <t>wallet.wallet_transaction</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>maintenance.asset</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -3733,11 +3733,11 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -3748,46 +3748,46 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>control.partner_agreement</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>control.partner_application</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>control.partner_change_request</t>
+          <t>control.partner_agreement</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>marketing.privacy_notice_governance</t>
+          <t>control.partner_application</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
@@ -3848,21 +3848,21 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>orders.cart_line</t>
+          <t>control.partner_change_request</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>orders, venue-map</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>marketing.privacy_notice_governance</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>approvals, marketing-crm</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
@@ -3898,21 +3898,21 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>orders.cart_line</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>orders, venue-map</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
@@ -3923,21 +3923,21 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>catalogue.product_version</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>catalogue, fnb</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
@@ -3948,17 +3948,17 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>seating.seat_hold_item</t>
+          <t>payments.routing_rule</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>catalogue, seating</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
@@ -3973,23 +3973,48 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>tenancy.data_retention_setting</t>
+          <t>seating.seat_hold_item</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>access, tenancy</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
         <v>2</v>
       </c>
       <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>tenancy.data_retention_setting</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>TenancyService</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>access, tenancy</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>115</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>138</v>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>77</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>132</v>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>catalogue, fnb, inventory, orders, payments, venue-map</t>
+          <t>catalogue, inventory, orders, payments, venue-map</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>access, ai, finance, games, marketing-crm, promotions +4</t>
+          <t>access, ai, finance, fnb, games, marketing-crm +5</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>approvals, finance, marketing-crm, platform-ops, public-api, subscription, tenancy, white-label</t>
+          <t>approvals, marketing-crm, platform-ops, public-api, subscription, tenancy, white-label</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>ai, finance</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, accreditation, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>catalogue.inventory_hold</t>
+          <t>catalogue.inventory_reservation</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -3198,7 +3198,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>inventory.stock_reservation</t>
+          <t>inventory.stock_earmark</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -3298,7 +3298,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>catalogue.product</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -3308,11 +3308,11 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>catalogue, fnb, inventory</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -3323,21 +3323,21 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>catalogue.product</t>
+          <t>platform.region_settings</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>finance, tenancy</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>platform.region_settings</t>
+          <t>orders.order_event</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>finance, tenancy</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -3373,21 +3373,21 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>orders.order_event</t>
+          <t>promotions.promotion_evaluation_trace</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>orders, promotions</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
@@ -3398,21 +3398,21 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>promotions.promotion_evaluation_trace</t>
+          <t>orders.refund</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>orders, promotions</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>orders.refund</t>
+          <t>payments.payment_attempt</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -3433,11 +3433,11 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>payments.payment_attempt</t>
+          <t>ledger.price_variance</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>finance, orders</t>
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
@@ -3473,21 +3473,21 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>ledger.price_variance</t>
+          <t>platform.dsar_request</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>finance, orders</t>
+          <t>cross-region, identity</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
@@ -3498,21 +3498,21 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>platform.dsar_request</t>
+          <t>identity.role_permission</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>cross-region, identity</t>
+          <t>identity, tenancy</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>identity.role_permission</t>
+          <t>identity.delegated_access</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -3533,22 +3533,22 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>identity, tenancy</t>
+          <t>identity, orders</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>identity.delegated_access</t>
+          <t>pii.subject</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -3558,61 +3558,61 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>identity, orders</t>
+          <t>identity, marketing-crm</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
+          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>pii.subject</t>
+          <t>seating.seat_reservation</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>control.invoice_line</t>
+          <t>inventory.count_line</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>finance, subscription</t>
+          <t>fnb, inventory</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -3623,17 +3623,17 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>seating.seat_hold</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>catalogue, seating</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
@@ -3648,21 +3648,21 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>inventory.count_line</t>
+          <t>wallet.wallet_transaction</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -3673,21 +3673,21 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>maintenance.asset</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
@@ -3698,32 +3698,32 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>maintenance.asset</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -3733,11 +3733,11 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -3748,46 +3748,46 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>ai.activity</t>
+          <t>control.partner_agreement</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>control.partner_application</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>control.partner_agreement</t>
+          <t>control.partner_change_request</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -3823,21 +3823,21 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>control.partner_application</t>
+          <t>marketing.privacy_notice_governance</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>approvals, marketing-crm</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
@@ -3848,21 +3848,21 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>control.partner_change_request</t>
+          <t>orders.cart_line</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>orders, venue-map</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3873,17 +3873,17 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>marketing.privacy_notice_governance</t>
+          <t>payments.routing_rule</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
@@ -3898,21 +3898,21 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>orders.cart_line</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>orders, venue-map</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>catalogue.product_version</t>
+          <t>seating.seat_reservation_item</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -3933,11 +3933,11 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>catalogue, fnb</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
@@ -3948,73 +3948,23 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>tenancy.data_retention_setting</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>access, tenancy</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>seating.seat_hold_item</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>CatalogueService</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>catalogue, seating</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="10" t="inlineStr">
-        <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>tenancy.data_retention_setting</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>TenancyService</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>access, tenancy</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>cross-region, identity, marketing-crm, reporting, subscription, tenancy +2</t>
+          <t>cross-region, marketing-crm, reporting, subscription, tenancy, venue-map +1</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>approvals, subscription, workforce</t>
+          <t>approvals, finance, identity, subscription, workforce</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>access, ai, finance, fnb, games, marketing-crm +5</t>
+          <t>access, ai, finance, fnb, games, marketing-crm +6</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>access, ai, catalogue, finance, promotions</t>
+          <t>access, ai, catalogue, finance, promotions, tenancy</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, cross-region, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -2521,12 +2521,12 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>access, games, orders, subscription</t>
+          <t>access, cross-region, games, orders, subscription</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>cross-region</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, promotions, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -2848,71 +2848,71 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>marketing.message_dispatch</t>
+          <t>platform.audit_record</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, public-api, workforce</t>
+          <t>finance, identity, inventory, orders, payments, platform-ops, tenancy</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>**Five writers, and every one is sending a message somebody asked for.** A verification email, a payment link, an evacuation notice.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>platform.audit_record</t>
+          <t>marketing.message_dispatch</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>finance, inventory, orders, payments, platform-ops, tenancy</t>
+          <t>fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**Five writers, and every one is sending a message somebody asked for.** A verification email, a payment link, an evacuation notice.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>catalogue.inventory_reservation</t>
+          <t>sync.rejection</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>catalogue, orders, payments, venue-map</t>
+          <t>access, cross-region, games, orders, subscription</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>orders.payment</t>
+          <t>approvals.request</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>orders, payments, subscription, wallet</t>
+          <t>approvals, finance, identity, subscription, workforce</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -2948,46 +2948,46 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ledger.journal_entry</t>
+          <t>catalogue.inventory_reservation</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>finance, orders, payments, shift</t>
+          <t>catalogue, orders, payments, venue-map</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>As above. The journal is written by whatever caused the money to move.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>sync.rejection</t>
+          <t>orders.payment</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>access, games, orders, subscription</t>
+          <t>orders, payments, subscription, wallet</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
@@ -2998,107 +2998,107 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>inventory.movement</t>
+          <t>ledger.journal_entry</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory, maintenance, retail</t>
+          <t>finance, orders, payments, shift</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
+          <t>As above. The journal is written by whatever caused the money to move.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>catalogue.channel_capacity</t>
+          <t>inventory.movement</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>catalogue, orders, payments</t>
+          <t>fnb, inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>access.entitlement</t>
+          <t>catalogue.channel_capacity</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>AccessService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>access, catalogue, orders</t>
+          <t>catalogue, orders, payments</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>orders.order_line</t>
+          <t>access.entitlement</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>AccessService</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>fnb, orders, subscription</t>
+          <t>access, catalogue, orders</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>orders.sales_order</t>
+          <t>orders.order_line</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3108,47 +3108,47 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>identity, orders, subscription</t>
+          <t>fnb, orders, subscription</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>ledger.posting</t>
+          <t>orders.sales_order</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>finance, orders, shift</t>
+          <t>identity, orders, subscription</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>**A till closing is a ledger act.** Settling a shift posts to the ledger, and a payment writes its own entry — appending, never redefining.</t>
+          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>ledger.journal_line</t>
+          <t>ledger.posting</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -3158,36 +3158,36 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>finance, orders, payments</t>
+          <t>finance, orders, shift</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**A till closing is a ledger act.** Settling a shift posts to the ledger, and a payment writes its own entry — appending, never redefining.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>marketing.consent_record</t>
+          <t>ledger.journal_line</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>access, marketing-crm, orders</t>
+          <t>finance, orders, payments</t>
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
@@ -3198,21 +3198,21 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>inventory.stock_earmark</t>
+          <t>marketing.consent_record</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>inventory, maintenance, retail</t>
+          <t>access, marketing-crm, orders</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -3223,21 +3223,21 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>approvals.request</t>
+          <t>inventory.stock_earmark</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription, workforce</t>
+          <t>inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -3473,25 +3473,25 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>platform.dsar_request</t>
+          <t>identity.delegated_access</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>cross-region, identity</t>
+          <t>identity, orders</t>
         </is>
       </c>
       <c r="D32" s="10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>identity.delegated_access</t>
+          <t>pii.subject</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -3533,61 +3533,61 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>identity, orders</t>
+          <t>identity, marketing-crm</t>
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>A share and a developer membership are both delegated authority (CF-132) — one mechanism, three callers.</t>
+          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>pii.subject</t>
+          <t>seating.seat_reservation</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>seating.seat_reservation</t>
+          <t>inventory.count_line</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>catalogue, seating</t>
+          <t>fnb, inventory</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>inventory.count_line</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -3608,11 +3608,11 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>wallet.wallet_transaction</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>maintenance.asset</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -3673,71 +3673,71 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>maintenance.asset</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>ai.activity</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>control.partner_agreement</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>control.partner_agreement</t>
+          <t>control.partner_application</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>control.partner_application</t>
+          <t>control.partner_change_request</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
@@ -3798,17 +3798,17 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>control.partner_change_request</t>
+          <t>marketing.privacy_notice_governance</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>approvals, marketing-crm</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
@@ -3823,21 +3823,21 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>marketing.privacy_notice_governance</t>
+          <t>orders.cart_line</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm</t>
+          <t>orders, venue-map</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>orders.cart_line</t>
+          <t>payments.routing_rule</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -3858,11 +3858,11 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>orders, venue-map</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3873,17 +3873,17 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
@@ -3898,17 +3898,17 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>platform.dead_letter</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>platform-ops, tenancy</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
@@ -3965,6 +3965,31 @@
         <v>2</v>
       </c>
       <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>pii.consent_identifier</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>IdentityService</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>identity, marketing-crm</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -661,7 +661,7 @@
         <v>213</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>41</v>
@@ -807,7 +807,7 @@
         <v>299</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>278</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>109</v>
@@ -1876,12 +1876,12 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>identity, orders, tenancy</t>
+          <t>identity, marketing-crm, orders, tenancy</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>access, approvals, fnb, marketing-crm, reporting, resources +4</t>
+          <t>access, approvals, fnb, reporting, resources, shift +3</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>pii.subject</t>
+          <t>identity.guest_session</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -3537,57 +3537,57 @@
         </is>
       </c>
       <c r="D34" s="10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>seating.seat_reservation</t>
+          <t>pii.subject</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>IdentityService</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>catalogue, seating</t>
+          <t>identity, marketing-crm</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**`identity` is the only real writer.** `marketing-crm` updates a profile field the subject owns — and consent never merges permissively (CF-160).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>inventory.count_line</t>
+          <t>seating.seat_reservation</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>fnb, inventory</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D36" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>inventory.requisition</t>
+          <t>inventory.count_line</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -3608,11 +3608,11 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>inventory, maintenance</t>
+          <t>fnb, inventory</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>wallet.wallet_transaction</t>
+          <t>inventory.requisition</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>WalletService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>orders, wallet</t>
+          <t>inventory, maintenance</t>
         </is>
       </c>
       <c r="D38" s="10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
@@ -3648,21 +3648,21 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>maintenance.asset</t>
+          <t>wallet.wallet_transaction</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>WalletService</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>maintenance, rental</t>
+          <t>orders, wallet</t>
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
@@ -3673,71 +3673,71 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>ai.activity</t>
+          <t>maintenance.asset</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>AiService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>ai, reporting</t>
+          <t>maintenance, rental</t>
         </is>
       </c>
       <c r="D40" s="10" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>ai.activity</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>AiService</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>ai, reporting</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**The governed reporting pair** (ADR-0020). `reporting` may write an AI interaction because a natural-language query is one.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>control.partner_agreement</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>control.partner_application</t>
+          <t>control.partner_agreement</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>control.partner_change_request</t>
+          <t>control.partner_application</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
@@ -3798,17 +3798,17 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>marketing.privacy_notice_governance</t>
+          <t>control.partner_change_request</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
@@ -3823,21 +3823,21 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>orders.cart_line</t>
+          <t>marketing.privacy_notice_governance</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>orders, venue-map</t>
+          <t>approvals, marketing-crm</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>orders.cart_line</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -3858,11 +3858,11 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>orders, venue-map</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3873,17 +3873,17 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>payments.routing_rule</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
@@ -3898,17 +3898,17 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>platform.dead_letter</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>platform-ops, tenancy</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
@@ -3923,17 +3923,17 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>seating.seat_reservation_item</t>
+          <t>platform.dead_letter</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>catalogue, seating</t>
+          <t>platform-ops, tenancy</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
@@ -3948,17 +3948,17 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>tenancy.data_retention_setting</t>
+          <t>seating.seat_reservation_item</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>access, tenancy</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
@@ -3973,23 +3973,48 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>pii.consent_identifier</t>
+          <t>tenancy.data_retention_setting</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>access, tenancy</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
         <v>2</v>
       </c>
       <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>pii.consent_identifier</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>IdentityService</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>identity, marketing-crm</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>105</v>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>114</v>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>229</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>approvals, finance, identity, subscription, workforce</t>
+          <t>approvals, finance, identity, subscription, white-label, workforce</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1771,12 +1771,12 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm, platform-ops, public-api, subscription, tenancy, white-label</t>
+          <t>approvals, marketing-crm, platform-ops, public-api, subscription, tenancy</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>ai, finance</t>
+          <t>finance, white-label</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>ai, public-api, retail, venue-map, workforce</t>
+          <t>ai, retail, venue-map, workforce</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>white-label</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr"/>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -2873,71 +2873,71 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>marketing.message_dispatch</t>
+          <t>approvals.request</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, public-api, workforce</t>
+          <t>approvals, finance, identity, subscription, white-label, workforce</t>
         </is>
       </c>
       <c r="D8" s="10" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>**Five writers, and every one is sending a message somebody asked for.** A verification email, a payment link, an evacuation notice.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>sync.rejection</t>
+          <t>marketing.message_dispatch</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>CrossRegionService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>access, cross-region, games, orders, subscription</t>
+          <t>fnb, identity, marketing-crm, orders, public-api, workforce</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**Five writers, and every one is sending a message somebody asked for.** A verification email, a payment link, an evacuation notice.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>approvals.request</t>
+          <t>sync.rejection</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CrossRegionService</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>approvals, finance, identity, subscription, workforce</t>
+          <t>access, cross-region, games, orders, subscription</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
@@ -2998,92 +2998,92 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>ledger.journal_entry</t>
+          <t>inventory.movement</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>LedgerService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>finance, orders, payments, shift</t>
+          <t>fnb, inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>As above. The journal is written by whatever caused the money to move.</t>
+          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>inventory.movement</t>
+          <t>catalogue.channel_capacity</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>fnb, inventory, maintenance, retail</t>
+          <t>catalogue, orders, payments</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>**Every stock change is a movement.** Waste from F&amp;B and adjustment from inventory are the same act with a different reason.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>catalogue.channel_capacity</t>
+          <t>access.entitlement</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>AccessService</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>catalogue, orders, payments</t>
+          <t>access, catalogue, orders</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>access.entitlement</t>
+          <t>orders.order_line</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>AccessService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>access, catalogue, orders</t>
+          <t>fnb, orders, subscription</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
@@ -3091,14 +3091,14 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>orders.order_line</t>
+          <t>orders.sales_order</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3108,40 +3108,40 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>fnb, orders, subscription</t>
+          <t>identity, orders, subscription</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>orders.sales_order</t>
+          <t>ledger.journal_entry</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>LedgerService</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>identity, orders, subscription</t>
+          <t>finance, orders, payments</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
+          <t>As above. The journal is written by whatever caused the money to move.</t>
         </is>
       </c>
     </row>
@@ -3198,21 +3198,21 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>marketing.consent_record</t>
+          <t>inventory.stock_earmark</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>InventoryService</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>access, marketing-crm, orders</t>
+          <t>inventory, maintenance, retail</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
@@ -3223,21 +3223,21 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>inventory.stock_earmark</t>
+          <t>orders.cart</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>InventoryService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>inventory, maintenance, retail</t>
+          <t>marketing-crm, orders, venue-map</t>
         </is>
       </c>
       <c r="D22" s="10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
@@ -3248,21 +3248,21 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>orders.cart</t>
+          <t>marketing.consent_record</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>marketing-crm, orders, venue-map</t>
+          <t>access, marketing-crm, orders</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
@@ -3848,21 +3848,21 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>orders.cart_line</t>
+          <t>approvals.matrix</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>orders, venue-map</t>
+          <t>approvals, white-label</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>orders.cart_line</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -3883,11 +3883,11 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>orders, venue-map</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
@@ -3898,17 +3898,17 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>payments.routing_rule</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
@@ -3923,17 +3923,17 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>platform.dead_letter</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>platform-ops, tenancy</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
@@ -3948,17 +3948,17 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>seating.seat_reservation_item</t>
+          <t>platform.dead_letter</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>catalogue, seating</t>
+          <t>platform-ops, tenancy</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
@@ -3973,17 +3973,17 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>tenancy.data_retention_setting</t>
+          <t>seating.seat_reservation_item</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>access, tenancy</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
@@ -3998,23 +3998,48 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>pii.consent_identifier</t>
+          <t>tenancy.data_retention_setting</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>access, tenancy</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>pii.consent_identifier</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>IdentityService</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>identity, marketing-crm</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -1811,7 +1811,7 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>ai, inventory, promotions</t>
+          <t>ai, inventory, promotions, reporting</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>catalogue, inventory, subscription</t>
+          <t>catalogue, inventory, reporting, subscription</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>ai, catalogue, promotions, queue, resources, white-label</t>
+          <t>ai, catalogue, promotions, queue, reporting, resources +1</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>access, ai, catalogue, finance, promotions, tenancy</t>
+          <t>access, ai, catalogue, finance, promotions, reporting +1</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>32</v>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -661,7 +661,7 @@
         <v>214</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>77</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>127</v>
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>110</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>catalogue, inventory, orders, payments, venue-map</t>
+          <t>catalogue, inventory, orders, payments, promotions, venue-map</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>access, ai, finance, fnb, games, marketing-crm +6</t>
+          <t>access, ai, finance, fnb, games, marketing-crm +5</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>fnb, identity, marketing-crm, orders, payments, resources, shift, subscription, venue-map, wallet</t>
+          <t>fnb, marketing-crm, orders, payments, resources, shift, subscription, venue-map, wallet</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, queue, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, promotions, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, promotions, queue, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>catalogue.channel_capacity</t>
+          <t>catalogue.product</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>catalogue, orders, payments</t>
+          <t>catalogue, inventory, promotions</t>
         </is>
       </c>
       <c r="D14" s="10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
@@ -3048,57 +3048,57 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>access.entitlement</t>
+          <t>catalogue.channel_capacity</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>AccessService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>access, catalogue, orders</t>
+          <t>catalogue, orders, payments</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>orders.order_line</t>
+          <t>access.entitlement</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>AccessService</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>fnb, orders, subscription</t>
+          <t>access, catalogue, orders</t>
         </is>
       </c>
       <c r="D16" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>**A sale issues a ticket.** `orders` appends the entitlement, `catalogue` suspends and freezes it against its template. Neither redefines the row.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>orders.sales_order</t>
+          <t>orders.order_line</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3108,15 +3108,15 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>identity, orders, subscription</t>
+          <t>fnb, orders, subscription</t>
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>
       </c>
     </row>
@@ -3298,21 +3298,21 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>catalogue.product</t>
+          <t>platform.region_settings</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>finance, tenancy</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
@@ -3323,21 +3323,21 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>platform.region_settings</t>
+          <t>orders.order_event</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>finance, tenancy</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D26" s="10" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>orders.order_event</t>
+          <t>orders.sales_order</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -3358,15 +3358,15 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>orders, subscription</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>Checked and correct — a side effect of the writing service's own job.</t>
+          <t>`identity` links a guest checkout to an existing order. One field, on claim.</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="D30" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>games.card</t>
+          <t>catalogue.variant</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>VenueOpsService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>games, wallet</t>
+          <t>catalogue, promotions</t>
         </is>
       </c>
       <c r="D42" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
@@ -3748,21 +3748,21 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>control.partner_agreement</t>
+          <t>games.card</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>PlatformService</t>
+          <t>VenueOpsService</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>approvals, subscription</t>
+          <t>games, wallet</t>
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>control.partner_application</t>
+          <t>control.partner_agreement</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="D44" s="10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>control.partner_change_request</t>
+          <t>control.partner_application</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
@@ -3823,17 +3823,17 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>marketing.privacy_notice_governance</t>
+          <t>control.partner_change_request</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>MarketingService</t>
+          <t>PlatformService</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>approvals, marketing-crm</t>
+          <t>approvals, subscription</t>
         </is>
       </c>
       <c r="D46" s="10" t="n">
@@ -3848,21 +3848,21 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>approvals.matrix</t>
+          <t>marketing.privacy_notice_governance</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>MarketingService</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>approvals, white-label</t>
+          <t>approvals, marketing-crm</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>orders.cart_line</t>
+          <t>approvals.matrix</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>OrderService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>orders, venue-map</t>
+          <t>approvals, white-label</t>
         </is>
       </c>
       <c r="D48" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>payments.routing_rule</t>
+          <t>orders.cart_line</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -3908,11 +3908,11 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>orders, payments</t>
+          <t>orders, venue-map</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
@@ -3923,17 +3923,17 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>catalogue.price</t>
+          <t>payments.routing_rule</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>OrderService</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>catalogue, inventory</t>
+          <t>orders, payments</t>
         </is>
       </c>
       <c r="D50" s="10" t="n">
@@ -3948,17 +3948,17 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>platform.dead_letter</t>
+          <t>catalogue.price</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>platform-ops, tenancy</t>
+          <t>catalogue, inventory</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
@@ -3973,17 +3973,17 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>seating.seat_reservation_item</t>
+          <t>platform.dead_letter</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>CatalogueService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>catalogue, seating</t>
+          <t>platform-ops, tenancy</t>
         </is>
       </c>
       <c r="D52" s="10" t="n">
@@ -3998,17 +3998,17 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>tenancy.data_retention_setting</t>
+          <t>seating.seat_reservation_item</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>TenancyService</t>
+          <t>CatalogueService</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>access, tenancy</t>
+          <t>catalogue, seating</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
@@ -4023,23 +4023,48 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>pii.consent_identifier</t>
+          <t>tenancy.data_retention_setting</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>IdentityService</t>
+          <t>TenancyService</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>identity, marketing-crm</t>
+          <t>access, tenancy</t>
         </is>
       </c>
       <c r="D54" s="10" t="n">
         <v>2</v>
       </c>
       <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Checked and correct — a side effect of the writing service's own job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>pii.consent_identifier</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>IdentityService</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>identity, marketing-crm</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>Checked and correct — a side effect of the writing service's own job.</t>
         </is>

--- a/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
+++ b/ticvai/repos/ticvai-contracts/project-bible/handoff/TICVAI_Services_and_Data_Segregation.xlsx
@@ -661,7 +661,7 @@
         <v>214</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="C17" s="10" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>110</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>ai, identity, maintenance, seating, tenancy, venue-map</t>
+          <t>ai, maintenance, seating, venue-map</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, queue, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, accreditation, approvals, assets, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, platform-ops, promotions, queue, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
@@ -2808,11 +2808,11 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>access, accreditation, approvals, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, promotions, queue, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
+          <t>access, accreditation, approvals, assets, catalogue, finance, fnb, identity, inventory, maintenance, marketing-crm, orders, payments, promotions, queue, reporting, seating, shift, subscription, tenancy, wallet, white-label</t>
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
